--- a/BD_MCAP.xlsx
+++ b/BD_MCAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcsfcomar.sharepoint.com/sites/grp_ces/Documentos compartidos/BD_sp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1005" documentId="13_ncr:1_{C2533B98-536A-43E9-9ACC-FF3779DD6A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB169188-E311-4FE8-B29C-E674547EB330}"/>
+  <xr:revisionPtr revIDLastSave="1035" documentId="13_ncr:1_{C2533B98-536A-43E9-9ACC-FF3779DD6A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6684A98-08F1-4BDD-A88C-DADD10116AA0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -542,7 +542,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -576,12 +576,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1249,9 +1243,6 @@
     <xf numFmtId="1" fontId="2" fillId="6" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="7" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="6" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
@@ -1430,6 +1421,9 @@
     <xf numFmtId="164" fontId="6" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1807,418 +1801,418 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="B1"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="65"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="64"/>
     </row>
     <row r="3" spans="1:26" ht="15" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66" t="s">
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="65"/>
+      <c r="F3" s="64"/>
     </row>
     <row r="4" spans="1:26" ht="15" x14ac:dyDescent="0.25">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66" t="s">
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="65"/>
+      <c r="F4" s="64"/>
     </row>
     <row r="5" spans="1:26" ht="15" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66" t="s">
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="65"/>
+      <c r="F5" s="64"/>
     </row>
     <row r="6" spans="1:26" ht="15" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66" t="s">
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="65"/>
+      <c r="F6" s="64"/>
     </row>
     <row r="7" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="65"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="65"/>
-    </row>
-    <row r="8" spans="1:26" s="69" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="68"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68" t="s">
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="64"/>
+    </row>
+    <row r="8" spans="1:26" s="68" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="67"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
     </row>
     <row r="9" spans="1:26" ht="1.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:26" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:26" s="96" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="93"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="94" t="s">
+    <row r="12" spans="1:26" s="95" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="92"/>
+      <c r="B12" s="92"/>
+      <c r="C12" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="95">
-        <v>46286</v>
-      </c>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95" t="s">
+      <c r="D12" s="94">
+        <v>46316</v>
+      </c>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="G12" s="95" t="str">
-        <f>"2026.08"</f>
-        <v>2026.08</v>
-      </c>
-      <c r="I12" s="93"/>
-      <c r="J12" s="93"/>
-      <c r="K12" s="93"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="93"/>
-      <c r="N12" s="93"/>
-      <c r="O12" s="93"/>
-      <c r="P12" s="93"/>
-      <c r="Q12" s="93"/>
-      <c r="R12" s="93"/>
-      <c r="S12" s="93"/>
-      <c r="T12" s="93"/>
-      <c r="U12" s="93"/>
-      <c r="V12" s="93"/>
-      <c r="W12" s="93"/>
-      <c r="X12" s="93"/>
-      <c r="Y12" s="93"/>
-      <c r="Z12" s="93"/>
-    </row>
-    <row r="14" spans="1:26" s="81" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="83"/>
-      <c r="C14" s="83" t="s">
+      <c r="G12" s="94" t="str">
+        <f>"2026.09"</f>
+        <v>2026.09</v>
+      </c>
+      <c r="I12" s="92"/>
+      <c r="J12" s="92"/>
+      <c r="K12" s="92"/>
+      <c r="L12" s="92"/>
+      <c r="M12" s="92"/>
+      <c r="N12" s="92"/>
+      <c r="O12" s="92"/>
+      <c r="P12" s="92"/>
+      <c r="Q12" s="92"/>
+      <c r="R12" s="92"/>
+      <c r="S12" s="92"/>
+      <c r="T12" s="92"/>
+      <c r="U12" s="92"/>
+      <c r="V12" s="92"/>
+      <c r="W12" s="92"/>
+      <c r="X12" s="92"/>
+      <c r="Y12" s="92"/>
+      <c r="Z12" s="92"/>
+    </row>
+    <row r="14" spans="1:26" s="80" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="82"/>
+      <c r="C14" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="83"/>
-    </row>
-    <row r="15" spans="1:26" s="82" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="84"/>
-      <c r="C15" s="84" t="s">
+      <c r="D14" s="82"/>
+    </row>
+    <row r="15" spans="1:26" s="81" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="83"/>
+      <c r="C15" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="84"/>
+      <c r="D15" s="83"/>
     </row>
     <row r="16" spans="1:26" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B17" s="33"/>
-      <c r="C17" s="92" t="s">
+      <c r="C17" s="91" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="2:8" s="70" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="91" t="s">
+    <row r="19" spans="2:8" s="69" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="85" t="s">
+      <c r="C19" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="F19" s="77" t="s">
+      <c r="F19" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70"/>
     </row>
     <row r="20" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="89">
+      <c r="B20" s="88">
         <v>1</v>
       </c>
-      <c r="C20" s="86" t="s">
+      <c r="C20" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="72"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="78" t="s">
+      <c r="D20" s="71"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="77" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="89">
+      <c r="B21" s="88">
         <v>2</v>
       </c>
-      <c r="C21" s="87" t="s">
+      <c r="C21" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="66"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="79" t="s">
+      <c r="D21" s="65"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="78" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="89">
+      <c r="B22" s="88">
         <v>3</v>
       </c>
-      <c r="C22" s="87" t="s">
+      <c r="C22" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="66"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="79" t="s">
+      <c r="D22" s="65"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="78" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="89">
+      <c r="B23" s="88">
         <v>4</v>
       </c>
-      <c r="C23" s="87" t="s">
+      <c r="C23" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="66"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="79" t="s">
+      <c r="D23" s="65"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="78" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="89">
+      <c r="B24" s="88">
         <v>5</v>
       </c>
-      <c r="C24" s="87" t="s">
+      <c r="C24" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="66"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="79" t="s">
+      <c r="D24" s="65"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="78" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="89">
+      <c r="B25" s="88">
         <v>6</v>
       </c>
-      <c r="C25" s="87" t="s">
+      <c r="C25" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="66"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="79" t="s">
+      <c r="D25" s="65"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="78" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="89">
+      <c r="B26" s="88">
         <v>7</v>
       </c>
-      <c r="C26" s="87" t="s">
+      <c r="C26" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="66"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="79" t="s">
+      <c r="D26" s="65"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="78" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="89">
+      <c r="B27" s="88">
         <v>8</v>
       </c>
-      <c r="C27" s="87" t="s">
+      <c r="C27" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="66"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="79" t="s">
+      <c r="D27" s="65"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="78" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="89">
+      <c r="B28" s="88">
         <v>9</v>
       </c>
-      <c r="C28" s="87" t="s">
+      <c r="C28" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="66"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="79" t="s">
+      <c r="D28" s="65"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="78" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="89">
+      <c r="B29" s="88">
         <v>10</v>
       </c>
-      <c r="C29" s="87" t="s">
+      <c r="C29" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="66"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="79" t="s">
+      <c r="D29" s="65"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="78" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="89">
+      <c r="B30" s="88">
         <v>11</v>
       </c>
-      <c r="C30" s="87" t="s">
+      <c r="C30" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="66"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="79" t="s">
+      <c r="D30" s="65"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="78" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="31" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="89">
+      <c r="B31" s="88">
         <v>12</v>
       </c>
-      <c r="C31" s="87" t="s">
+      <c r="C31" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="66"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="79" t="s">
+      <c r="D31" s="65"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="78" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="32" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="89">
+      <c r="B32" s="88">
         <v>13</v>
       </c>
-      <c r="C32" s="87" t="s">
+      <c r="C32" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="66"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="79" t="s">
+      <c r="D32" s="65"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="78" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="33" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="89">
+      <c r="B33" s="88">
         <v>14</v>
       </c>
-      <c r="C33" s="87" t="s">
+      <c r="C33" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="D33" s="66"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="79" t="s">
+      <c r="D33" s="65"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="78" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="34" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="89">
+      <c r="B34" s="88">
         <v>15</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="86" t="s">
         <v>62</v>
       </c>
-      <c r="D34" s="66"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="79" t="s">
+      <c r="D34" s="65"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="78" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="35" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="89">
+      <c r="B35" s="88">
         <v>16</v>
       </c>
-      <c r="C35" s="87" t="s">
+      <c r="C35" s="86" t="s">
         <v>63</v>
       </c>
-      <c r="D35" s="66"/>
-      <c r="E35" s="74"/>
-      <c r="F35" s="79" t="s">
+      <c r="D35" s="65"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="78" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="36" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="89">
+      <c r="B36" s="88">
         <v>17</v>
       </c>
-      <c r="C36" s="87" t="s">
+      <c r="C36" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="D36" s="66"/>
-      <c r="E36" s="74"/>
-      <c r="F36" s="79" t="s">
+      <c r="D36" s="65"/>
+      <c r="E36" s="73"/>
+      <c r="F36" s="78" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="89">
+      <c r="B37" s="88">
         <v>18</v>
       </c>
-      <c r="C37" s="87" t="s">
+      <c r="C37" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="D37" s="66"/>
-      <c r="E37" s="74"/>
-      <c r="F37" s="79" t="s">
+      <c r="D37" s="65"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="78" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="38" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="89">
+      <c r="B38" s="88">
         <v>19</v>
       </c>
-      <c r="C38" s="87" t="s">
+      <c r="C38" s="86" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="66"/>
-      <c r="E38" s="74"/>
-      <c r="F38" s="79" t="s">
+      <c r="D38" s="65"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="78" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="39" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="89">
+      <c r="B39" s="88">
         <v>20</v>
       </c>
-      <c r="C39" s="87" t="s">
+      <c r="C39" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="66"/>
-      <c r="E39" s="74"/>
-      <c r="F39" s="79" t="s">
+      <c r="D39" s="65"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="78" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="90">
+      <c r="B40" s="89">
         <v>21</v>
       </c>
-      <c r="C40" s="88" t="s">
+      <c r="C40" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="D40" s="75"/>
-      <c r="E40" s="76"/>
-      <c r="F40" s="80" t="s">
+      <c r="D40" s="74"/>
+      <c r="E40" s="75"/>
+      <c r="F40" s="79" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2268,36 +2262,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="131" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="103"/>
-      <c r="R1" s="103"/>
-      <c r="S1" s="103"/>
-      <c r="T1" s="103"/>
-      <c r="U1" s="103"/>
-      <c r="V1" s="104"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="103"/>
     </row>
     <row r="2" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="104" t="s">
         <v>60</v>
       </c>
       <c r="C2" s="4"/>
@@ -2307,13 +2301,13 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="106"/>
-      <c r="K2" s="106"/>
-      <c r="L2" s="106"/>
-      <c r="M2" s="106"/>
-      <c r="N2" s="106"/>
-      <c r="O2" s="107"/>
-      <c r="P2" s="105" t="s">
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="105"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="104" t="s">
         <v>61</v>
       </c>
       <c r="Q2" s="4"/>
@@ -2321,13 +2315,13 @@
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
-      <c r="V2" s="108"/>
+      <c r="V2" s="107"/>
     </row>
     <row r="3" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="108" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="3"/>
@@ -2337,13 +2331,13 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="25"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="107"/>
-      <c r="P3" s="109" t="s">
+      <c r="J3" s="105"/>
+      <c r="K3" s="105"/>
+      <c r="L3" s="105"/>
+      <c r="M3" s="105"/>
+      <c r="N3" s="105"/>
+      <c r="O3" s="106"/>
+      <c r="P3" s="108" t="s">
         <v>24</v>
       </c>
       <c r="Q3" s="3"/>
@@ -2354,7 +2348,7 @@
       <c r="V3" s="7"/>
     </row>
     <row r="4" spans="1:22" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="118" t="s">
+      <c r="A4" s="117" t="s">
         <v>77</v>
       </c>
       <c r="B4" s="37" t="s">
@@ -2367,7 +2361,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="61" t="s">
+      <c r="J4" s="60" t="s">
         <v>26</v>
       </c>
       <c r="K4" s="19"/>
@@ -2377,7 +2371,7 @@
         <v>27</v>
       </c>
       <c r="O4" s="38"/>
-      <c r="P4" s="61" t="s">
+      <c r="P4" s="60" t="s">
         <v>49</v>
       </c>
       <c r="Q4" s="19"/>
@@ -2385,10 +2379,10 @@
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
-      <c r="V4" s="63"/>
+      <c r="V4" s="62"/>
     </row>
     <row r="5" spans="1:22" ht="45" x14ac:dyDescent="0.2">
-      <c r="A5" s="118" t="s">
+      <c r="A5" s="117" t="s">
         <v>78</v>
       </c>
       <c r="B5" s="47" t="s">
@@ -2448,15 +2442,15 @@
       <c r="T5" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="U5" s="125" t="s">
+      <c r="U5" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="V5" s="126" t="s">
+      <c r="V5" s="125" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="117" t="s">
         <v>83</v>
       </c>
       <c r="B6" s="34"/>
@@ -2472,7 +2466,7 @@
       <c r="L6" s="35"/>
       <c r="M6" s="35"/>
       <c r="N6" s="35"/>
-      <c r="O6" s="55"/>
+      <c r="O6" s="54"/>
       <c r="P6" s="34"/>
       <c r="Q6" s="34"/>
       <c r="R6" s="34"/>
@@ -2513,141 +2507,141 @@
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
-      <c r="V7" s="63"/>
+      <c r="V7" s="62"/>
     </row>
     <row r="8" spans="1:22" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="118" t="s">
+      <c r="A8" s="117" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="121" t="s">
+      <c r="B8" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="121" t="s">
+      <c r="C8" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="121" t="s">
+      <c r="D8" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="121" t="s">
+      <c r="E8" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="F8" s="121" t="s">
+      <c r="F8" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="121" t="s">
+      <c r="G8" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="H8" s="121" t="s">
+      <c r="H8" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="I8" s="121" t="s">
+      <c r="I8" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="J8" s="121" t="s">
+      <c r="J8" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="K8" s="121" t="s">
+      <c r="K8" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="L8" s="121" t="s">
+      <c r="L8" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="M8" s="121" t="s">
+      <c r="M8" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="N8" s="122" t="s">
+      <c r="N8" s="121" t="s">
         <v>82</v>
       </c>
-      <c r="O8" s="123" t="s">
+      <c r="O8" s="122" t="s">
         <v>82</v>
       </c>
-      <c r="P8" s="121" t="s">
+      <c r="P8" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="Q8" s="121" t="s">
+      <c r="Q8" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="R8" s="121" t="s">
+      <c r="R8" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="S8" s="121" t="s">
+      <c r="S8" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="T8" s="121" t="s">
+      <c r="T8" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="U8" s="121" t="s">
+      <c r="U8" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="V8" s="124" t="s">
+      <c r="V8" s="123" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="119" t="s">
+      <c r="B9" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="110" t="s">
+      <c r="C9" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="111" t="s">
+      <c r="D9" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="110" t="s">
+      <c r="E9" s="109" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="111" t="s">
+      <c r="F9" s="110" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="110" t="s">
+      <c r="G9" s="109" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="111" t="s">
+      <c r="H9" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="I9" s="112" t="s">
+      <c r="I9" s="111" t="s">
         <v>42</v>
       </c>
-      <c r="J9" s="113" t="s">
+      <c r="J9" s="112" t="s">
         <v>59</v>
       </c>
-      <c r="K9" s="111" t="s">
+      <c r="K9" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="L9" s="110" t="s">
+      <c r="L9" s="109" t="s">
         <v>44</v>
       </c>
-      <c r="M9" s="110" t="s">
+      <c r="M9" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="N9" s="113" t="s">
+      <c r="N9" s="112" t="s">
         <v>46</v>
       </c>
-      <c r="O9" s="114" t="s">
+      <c r="O9" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="P9" s="115" t="s">
+      <c r="P9" s="114" t="s">
         <v>48</v>
       </c>
-      <c r="Q9" s="115" t="s">
+      <c r="Q9" s="114" t="s">
         <v>53</v>
       </c>
-      <c r="R9" s="115" t="s">
+      <c r="R9" s="114" t="s">
         <v>54</v>
       </c>
-      <c r="S9" s="115" t="s">
+      <c r="S9" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="T9" s="115" t="s">
+      <c r="T9" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="U9" s="115" t="s">
+      <c r="U9" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="V9" s="116" t="s">
+      <c r="V9" s="115" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2658,10 +2652,10 @@
       <c r="B10" s="49">
         <v>0</v>
       </c>
-      <c r="C10" s="120">
+      <c r="C10" s="119">
         <v>530.22</v>
       </c>
-      <c r="D10" s="120">
+      <c r="D10" s="119">
         <v>17.59</v>
       </c>
       <c r="E10" s="18">
@@ -2670,10 +2664,10 @@
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
       <c r="H10" s="20"/>
-      <c r="I10" s="60">
+      <c r="I10" s="59">
         <v>626.2600000000001</v>
       </c>
-      <c r="J10" s="117">
+      <c r="J10" s="116">
         <v>13</v>
       </c>
       <c r="K10" s="42">
@@ -2684,7 +2678,7 @@
       </c>
       <c r="M10" s="48"/>
       <c r="N10" s="14"/>
-      <c r="O10" s="56"/>
+      <c r="O10" s="55"/>
       <c r="P10" s="14"/>
       <c r="Q10" s="20"/>
       <c r="R10" s="20"/>
@@ -2715,7 +2709,7 @@
       <c r="I11" s="21">
         <v>628.68000000000006</v>
       </c>
-      <c r="J11" s="62">
+      <c r="J11" s="61">
         <v>14</v>
       </c>
       <c r="K11" s="9">
@@ -2726,7 +2720,7 @@
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="10"/>
-      <c r="O11" s="56"/>
+      <c r="O11" s="55"/>
       <c r="P11" s="14"/>
       <c r="Q11" s="20"/>
       <c r="R11" s="20"/>
@@ -2757,7 +2751,7 @@
       <c r="I12" s="21">
         <v>1241.21</v>
       </c>
-      <c r="J12" s="62">
+      <c r="J12" s="61">
         <v>15</v>
       </c>
       <c r="K12" s="9">
@@ -2768,7 +2762,7 @@
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="10"/>
-      <c r="O12" s="56"/>
+      <c r="O12" s="55"/>
       <c r="P12" s="14"/>
       <c r="Q12" s="20"/>
       <c r="R12" s="20"/>
@@ -2799,7 +2793,7 @@
       <c r="I13" s="21">
         <v>2995.625</v>
       </c>
-      <c r="J13" s="62">
+      <c r="J13" s="61">
         <v>17</v>
       </c>
       <c r="K13" s="9">
@@ -2810,7 +2804,7 @@
       </c>
       <c r="M13" s="22"/>
       <c r="N13" s="10"/>
-      <c r="O13" s="56"/>
+      <c r="O13" s="55"/>
       <c r="P13" s="14"/>
       <c r="Q13" s="20"/>
       <c r="R13" s="20"/>
@@ -2841,7 +2835,7 @@
       <c r="I14" s="21">
         <v>703.03</v>
       </c>
-      <c r="J14" s="62">
+      <c r="J14" s="61">
         <v>15</v>
       </c>
       <c r="K14" s="9">
@@ -2852,7 +2846,7 @@
       </c>
       <c r="M14" s="22"/>
       <c r="N14" s="10"/>
-      <c r="O14" s="56"/>
+      <c r="O14" s="55"/>
       <c r="P14" s="14"/>
       <c r="Q14" s="20"/>
       <c r="R14" s="20"/>
@@ -2883,7 +2877,7 @@
       <c r="I15" s="21">
         <v>1123.18</v>
       </c>
-      <c r="J15" s="62">
+      <c r="J15" s="61">
         <v>12</v>
       </c>
       <c r="K15" s="9">
@@ -2894,7 +2888,7 @@
       </c>
       <c r="M15" s="22"/>
       <c r="N15" s="10"/>
-      <c r="O15" s="56"/>
+      <c r="O15" s="55"/>
       <c r="P15" s="14"/>
       <c r="Q15" s="20"/>
       <c r="R15" s="20"/>
@@ -2925,7 +2919,7 @@
       <c r="I16" s="21">
         <v>7956.41</v>
       </c>
-      <c r="J16" s="62">
+      <c r="J16" s="61">
         <v>16</v>
       </c>
       <c r="K16" s="9">
@@ -2936,7 +2930,7 @@
       </c>
       <c r="M16" s="22"/>
       <c r="N16" s="10"/>
-      <c r="O16" s="56"/>
+      <c r="O16" s="55"/>
       <c r="P16" s="14"/>
       <c r="Q16" s="20"/>
       <c r="R16" s="20"/>
@@ -2967,7 +2961,7 @@
       <c r="I17" s="21">
         <v>951.59</v>
       </c>
-      <c r="J17" s="62">
+      <c r="J17" s="61">
         <v>14</v>
       </c>
       <c r="K17" s="9">
@@ -2978,7 +2972,7 @@
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="10"/>
-      <c r="O17" s="56"/>
+      <c r="O17" s="55"/>
       <c r="P17" s="14"/>
       <c r="Q17" s="20"/>
       <c r="R17" s="20"/>
@@ -3009,7 +3003,7 @@
       <c r="I18" s="21">
         <v>1145.05</v>
       </c>
-      <c r="J18" s="62">
+      <c r="J18" s="61">
         <v>14</v>
       </c>
       <c r="K18" s="9">
@@ -3020,7 +3014,7 @@
       </c>
       <c r="M18" s="22"/>
       <c r="N18" s="10"/>
-      <c r="O18" s="56"/>
+      <c r="O18" s="55"/>
       <c r="P18" s="14"/>
       <c r="Q18" s="20"/>
       <c r="R18" s="20"/>
@@ -3051,7 +3045,7 @@
       <c r="I19" s="21">
         <v>1711.69</v>
       </c>
-      <c r="J19" s="62">
+      <c r="J19" s="61">
         <v>15</v>
       </c>
       <c r="K19" s="9">
@@ -3062,7 +3056,7 @@
       </c>
       <c r="M19" s="22"/>
       <c r="N19" s="10"/>
-      <c r="O19" s="56"/>
+      <c r="O19" s="55"/>
       <c r="P19" s="14"/>
       <c r="Q19" s="20"/>
       <c r="R19" s="20"/>
@@ -3093,7 +3087,7 @@
       <c r="I20" s="21">
         <v>2986.2400000000002</v>
       </c>
-      <c r="J20" s="62">
+      <c r="J20" s="61">
         <v>17</v>
       </c>
       <c r="K20" s="9">
@@ -3104,7 +3098,7 @@
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="10"/>
-      <c r="O20" s="56"/>
+      <c r="O20" s="55"/>
       <c r="P20" s="14"/>
       <c r="Q20" s="20"/>
       <c r="R20" s="20"/>
@@ -3135,7 +3129,7 @@
       <c r="I21" s="21">
         <v>3656.1239999999998</v>
       </c>
-      <c r="J21" s="62">
+      <c r="J21" s="61">
         <v>27</v>
       </c>
       <c r="K21" s="9">
@@ -3146,7 +3140,7 @@
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="10"/>
-      <c r="O21" s="56"/>
+      <c r="O21" s="55"/>
       <c r="P21" s="14"/>
       <c r="Q21" s="20"/>
       <c r="R21" s="20"/>
@@ -3177,7 +3171,7 @@
       <c r="I22" s="21">
         <v>1602.81</v>
       </c>
-      <c r="J22" s="62">
+      <c r="J22" s="61">
         <v>15</v>
       </c>
       <c r="K22" s="9">
@@ -3188,7 +3182,7 @@
       </c>
       <c r="M22" s="22"/>
       <c r="N22" s="10"/>
-      <c r="O22" s="56"/>
+      <c r="O22" s="55"/>
       <c r="P22" s="14"/>
       <c r="Q22" s="20"/>
       <c r="R22" s="20"/>
@@ -3219,7 +3213,7 @@
       <c r="I23" s="21">
         <v>1662.77</v>
       </c>
-      <c r="J23" s="62">
+      <c r="J23" s="61">
         <v>19</v>
       </c>
       <c r="K23" s="9">
@@ -3230,7 +3224,7 @@
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="10"/>
-      <c r="O23" s="56"/>
+      <c r="O23" s="55"/>
       <c r="P23" s="14"/>
       <c r="Q23" s="20"/>
       <c r="R23" s="20"/>
@@ -3261,7 +3255,7 @@
       <c r="I24" s="21">
         <v>2440.7500000000005</v>
       </c>
-      <c r="J24" s="62">
+      <c r="J24" s="61">
         <v>16</v>
       </c>
       <c r="K24" s="9">
@@ -3272,7 +3266,7 @@
       </c>
       <c r="M24" s="22"/>
       <c r="N24" s="10"/>
-      <c r="O24" s="56"/>
+      <c r="O24" s="55"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="20"/>
       <c r="R24" s="20"/>
@@ -3303,7 +3297,7 @@
       <c r="I25" s="21">
         <v>6888.24</v>
       </c>
-      <c r="J25" s="62">
+      <c r="J25" s="61">
         <v>14</v>
       </c>
       <c r="K25" s="9">
@@ -3314,7 +3308,7 @@
       </c>
       <c r="M25" s="22"/>
       <c r="N25" s="10"/>
-      <c r="O25" s="56"/>
+      <c r="O25" s="55"/>
       <c r="P25" s="14"/>
       <c r="Q25" s="20"/>
       <c r="R25" s="20"/>
@@ -3345,7 +3339,7 @@
       <c r="I26" s="21">
         <v>3448.63</v>
       </c>
-      <c r="J26" s="62">
+      <c r="J26" s="61">
         <v>20</v>
       </c>
       <c r="K26" s="9">
@@ -3356,7 +3350,7 @@
       </c>
       <c r="M26" s="22"/>
       <c r="N26" s="10"/>
-      <c r="O26" s="56"/>
+      <c r="O26" s="55"/>
       <c r="P26" s="14"/>
       <c r="Q26" s="20"/>
       <c r="R26" s="20"/>
@@ -3387,7 +3381,7 @@
       <c r="I27" s="21">
         <v>1785.23</v>
       </c>
-      <c r="J27" s="62">
+      <c r="J27" s="61">
         <v>20</v>
       </c>
       <c r="K27" s="9">
@@ -3398,7 +3392,7 @@
       </c>
       <c r="M27" s="22"/>
       <c r="N27" s="10"/>
-      <c r="O27" s="56"/>
+      <c r="O27" s="55"/>
       <c r="P27" s="14"/>
       <c r="Q27" s="20"/>
       <c r="R27" s="20"/>
@@ -3429,7 +3423,7 @@
       <c r="I28" s="21">
         <v>1328.71</v>
       </c>
-      <c r="J28" s="62">
+      <c r="J28" s="61">
         <v>15</v>
       </c>
       <c r="K28" s="9">
@@ -3440,7 +3434,7 @@
       </c>
       <c r="M28" s="22"/>
       <c r="N28" s="10"/>
-      <c r="O28" s="56"/>
+      <c r="O28" s="55"/>
       <c r="P28" s="14"/>
       <c r="Q28" s="20"/>
       <c r="R28" s="20"/>
@@ -3471,7 +3465,7 @@
       <c r="I29" s="21">
         <v>2411.1700000000005</v>
       </c>
-      <c r="J29" s="62">
+      <c r="J29" s="61">
         <v>19</v>
       </c>
       <c r="K29" s="9">
@@ -3482,7 +3476,7 @@
       </c>
       <c r="M29" s="22"/>
       <c r="N29" s="10"/>
-      <c r="O29" s="56"/>
+      <c r="O29" s="55"/>
       <c r="P29" s="14"/>
       <c r="Q29" s="20"/>
       <c r="R29" s="20"/>
@@ -3513,7 +3507,7 @@
       <c r="I30" s="21">
         <v>2555.1099999999997</v>
       </c>
-      <c r="J30" s="62">
+      <c r="J30" s="61">
         <v>23</v>
       </c>
       <c r="K30" s="9">
@@ -3524,7 +3518,7 @@
       </c>
       <c r="M30" s="22"/>
       <c r="N30" s="10"/>
-      <c r="O30" s="56"/>
+      <c r="O30" s="55"/>
       <c r="P30" s="14"/>
       <c r="Q30" s="20"/>
       <c r="R30" s="20"/>
@@ -3555,7 +3549,7 @@
       <c r="I31" s="21">
         <v>1301.75</v>
       </c>
-      <c r="J31" s="62">
+      <c r="J31" s="61">
         <v>12</v>
       </c>
       <c r="K31" s="9">
@@ -3566,7 +3560,7 @@
       </c>
       <c r="M31" s="22"/>
       <c r="N31" s="10"/>
-      <c r="O31" s="56"/>
+      <c r="O31" s="55"/>
       <c r="P31" s="14"/>
       <c r="Q31" s="20"/>
       <c r="R31" s="20"/>
@@ -3597,7 +3591,7 @@
       <c r="I32" s="21">
         <v>1496.81</v>
       </c>
-      <c r="J32" s="62">
+      <c r="J32" s="61">
         <v>18</v>
       </c>
       <c r="K32" s="9">
@@ -3608,7 +3602,7 @@
       </c>
       <c r="M32" s="22"/>
       <c r="N32" s="10"/>
-      <c r="O32" s="56"/>
+      <c r="O32" s="55"/>
       <c r="P32" s="14"/>
       <c r="Q32" s="20"/>
       <c r="R32" s="20"/>
@@ -3639,7 +3633,7 @@
       <c r="I33" s="21">
         <v>2770.83</v>
       </c>
-      <c r="J33" s="62">
+      <c r="J33" s="61">
         <v>25</v>
       </c>
       <c r="K33" s="9">
@@ -3650,7 +3644,7 @@
       </c>
       <c r="M33" s="22"/>
       <c r="N33" s="10"/>
-      <c r="O33" s="56"/>
+      <c r="O33" s="55"/>
       <c r="P33" s="14"/>
       <c r="Q33" s="20"/>
       <c r="R33" s="20"/>
@@ -3681,7 +3675,7 @@
       <c r="I34" s="21">
         <v>1738.7599999999998</v>
       </c>
-      <c r="J34" s="62">
+      <c r="J34" s="61">
         <v>16</v>
       </c>
       <c r="K34" s="9">
@@ -3692,7 +3686,7 @@
       </c>
       <c r="M34" s="22"/>
       <c r="N34" s="10"/>
-      <c r="O34" s="56"/>
+      <c r="O34" s="55"/>
       <c r="P34" s="14"/>
       <c r="Q34" s="20"/>
       <c r="R34" s="20"/>
@@ -3723,7 +3717,7 @@
       <c r="I35" s="21">
         <v>1736.8</v>
       </c>
-      <c r="J35" s="62">
+      <c r="J35" s="61">
         <v>15</v>
       </c>
       <c r="K35" s="9">
@@ -3734,7 +3728,7 @@
       </c>
       <c r="M35" s="22"/>
       <c r="N35" s="10"/>
-      <c r="O35" s="56"/>
+      <c r="O35" s="55"/>
       <c r="P35" s="14"/>
       <c r="Q35" s="20"/>
       <c r="R35" s="20"/>
@@ -3765,7 +3759,7 @@
       <c r="I36" s="21">
         <v>1604.07</v>
       </c>
-      <c r="J36" s="62">
+      <c r="J36" s="61">
         <v>11</v>
       </c>
       <c r="K36" s="9">
@@ -3776,7 +3770,7 @@
       </c>
       <c r="M36" s="22"/>
       <c r="N36" s="10"/>
-      <c r="O36" s="56"/>
+      <c r="O36" s="55"/>
       <c r="P36" s="14"/>
       <c r="Q36" s="20"/>
       <c r="R36" s="20"/>
@@ -3807,7 +3801,7 @@
       <c r="I37" s="21">
         <v>2086.6999999999998</v>
       </c>
-      <c r="J37" s="62">
+      <c r="J37" s="61">
         <v>15</v>
       </c>
       <c r="K37" s="9">
@@ -3818,7 +3812,7 @@
       </c>
       <c r="M37" s="22"/>
       <c r="N37" s="10"/>
-      <c r="O37" s="56"/>
+      <c r="O37" s="55"/>
       <c r="P37" s="14"/>
       <c r="Q37" s="20"/>
       <c r="R37" s="20"/>
@@ -3849,7 +3843,7 @@
       <c r="I38" s="21">
         <v>4538.57</v>
       </c>
-      <c r="J38" s="62">
+      <c r="J38" s="61">
         <v>24</v>
       </c>
       <c r="K38" s="9">
@@ -3860,7 +3854,7 @@
       </c>
       <c r="M38" s="22"/>
       <c r="N38" s="10"/>
-      <c r="O38" s="56"/>
+      <c r="O38" s="55"/>
       <c r="P38" s="14"/>
       <c r="Q38" s="20"/>
       <c r="R38" s="20"/>
@@ -3891,7 +3885,7 @@
       <c r="I39" s="21">
         <v>1422.03</v>
       </c>
-      <c r="J39" s="62">
+      <c r="J39" s="61">
         <v>8</v>
       </c>
       <c r="K39" s="9">
@@ -3902,7 +3896,7 @@
       </c>
       <c r="M39" s="22"/>
       <c r="N39" s="10"/>
-      <c r="O39" s="56"/>
+      <c r="O39" s="55"/>
       <c r="P39" s="14"/>
       <c r="Q39" s="20"/>
       <c r="R39" s="20"/>
@@ -3933,7 +3927,7 @@
       <c r="I40" s="21">
         <v>1965.23</v>
       </c>
-      <c r="J40" s="62">
+      <c r="J40" s="61">
         <v>17</v>
       </c>
       <c r="K40" s="9">
@@ -3944,7 +3938,7 @@
       </c>
       <c r="M40" s="22"/>
       <c r="N40" s="10"/>
-      <c r="O40" s="56"/>
+      <c r="O40" s="55"/>
       <c r="P40" s="14"/>
       <c r="Q40" s="20"/>
       <c r="R40" s="20"/>
@@ -3975,7 +3969,7 @@
       <c r="I41" s="21">
         <v>3577.35</v>
       </c>
-      <c r="J41" s="62">
+      <c r="J41" s="61">
         <v>19</v>
       </c>
       <c r="K41" s="9">
@@ -3986,7 +3980,7 @@
       </c>
       <c r="M41" s="22"/>
       <c r="N41" s="10"/>
-      <c r="O41" s="56"/>
+      <c r="O41" s="55"/>
       <c r="P41" s="14"/>
       <c r="Q41" s="20"/>
       <c r="R41" s="20"/>
@@ -4017,7 +4011,7 @@
       <c r="I42" s="21">
         <v>3994.58</v>
       </c>
-      <c r="J42" s="62">
+      <c r="J42" s="61">
         <v>19</v>
       </c>
       <c r="K42" s="9">
@@ -4028,7 +4022,7 @@
       </c>
       <c r="M42" s="22"/>
       <c r="N42" s="10"/>
-      <c r="O42" s="56"/>
+      <c r="O42" s="55"/>
       <c r="P42" s="14"/>
       <c r="Q42" s="20"/>
       <c r="R42" s="20"/>
@@ -4059,7 +4053,7 @@
       <c r="I43" s="21">
         <v>3949.1600000000003</v>
       </c>
-      <c r="J43" s="62">
+      <c r="J43" s="61">
         <v>12</v>
       </c>
       <c r="K43" s="9">
@@ -4070,7 +4064,7 @@
       </c>
       <c r="M43" s="22"/>
       <c r="N43" s="10"/>
-      <c r="O43" s="56"/>
+      <c r="O43" s="55"/>
       <c r="P43" s="14"/>
       <c r="Q43" s="20"/>
       <c r="R43" s="20"/>
@@ -4101,7 +4095,7 @@
       <c r="I44" s="21">
         <v>5414.3400000000011</v>
       </c>
-      <c r="J44" s="62">
+      <c r="J44" s="61">
         <v>23</v>
       </c>
       <c r="K44" s="9">
@@ -4112,7 +4106,7 @@
       </c>
       <c r="M44" s="22"/>
       <c r="N44" s="10"/>
-      <c r="O44" s="56"/>
+      <c r="O44" s="55"/>
       <c r="P44" s="14"/>
       <c r="Q44" s="20"/>
       <c r="R44" s="20"/>
@@ -4143,7 +4137,7 @@
       <c r="I45" s="21">
         <v>6486.0999999999995</v>
       </c>
-      <c r="J45" s="62">
+      <c r="J45" s="61">
         <v>21</v>
       </c>
       <c r="K45" s="9">
@@ -4154,7 +4148,7 @@
       </c>
       <c r="M45" s="22"/>
       <c r="N45" s="10"/>
-      <c r="O45" s="56"/>
+      <c r="O45" s="55"/>
       <c r="P45" s="14"/>
       <c r="Q45" s="20"/>
       <c r="R45" s="20"/>
@@ -4185,7 +4179,7 @@
       <c r="I46" s="21">
         <v>2855.32</v>
       </c>
-      <c r="J46" s="62">
+      <c r="J46" s="61">
         <v>19</v>
       </c>
       <c r="K46" s="9">
@@ -4196,7 +4190,7 @@
       </c>
       <c r="M46" s="22"/>
       <c r="N46" s="10"/>
-      <c r="O46" s="56"/>
+      <c r="O46" s="55"/>
       <c r="P46" s="14"/>
       <c r="Q46" s="20"/>
       <c r="R46" s="20"/>
@@ -4227,7 +4221,7 @@
       <c r="I47" s="21">
         <v>3432.3999999999996</v>
       </c>
-      <c r="J47" s="62">
+      <c r="J47" s="61">
         <v>16</v>
       </c>
       <c r="K47" s="9">
@@ -4238,7 +4232,7 @@
       </c>
       <c r="M47" s="22"/>
       <c r="N47" s="10"/>
-      <c r="O47" s="56"/>
+      <c r="O47" s="55"/>
       <c r="P47" s="14"/>
       <c r="Q47" s="20"/>
       <c r="R47" s="20"/>
@@ -4269,7 +4263,7 @@
       <c r="I48" s="21">
         <v>4032.7000000000003</v>
       </c>
-      <c r="J48" s="62">
+      <c r="J48" s="61">
         <v>12</v>
       </c>
       <c r="K48" s="9">
@@ -4280,7 +4274,7 @@
       </c>
       <c r="M48" s="22"/>
       <c r="N48" s="10"/>
-      <c r="O48" s="56"/>
+      <c r="O48" s="55"/>
       <c r="P48" s="14"/>
       <c r="Q48" s="20"/>
       <c r="R48" s="20"/>
@@ -4311,7 +4305,7 @@
       <c r="I49" s="21">
         <v>6302.34</v>
       </c>
-      <c r="J49" s="62">
+      <c r="J49" s="61">
         <v>16</v>
       </c>
       <c r="K49" s="9">
@@ -4322,7 +4316,7 @@
       </c>
       <c r="M49" s="22"/>
       <c r="N49" s="10"/>
-      <c r="O49" s="56"/>
+      <c r="O49" s="55"/>
       <c r="P49" s="14"/>
       <c r="Q49" s="20"/>
       <c r="R49" s="20"/>
@@ -4353,7 +4347,7 @@
       <c r="I50" s="21">
         <v>4267.53</v>
       </c>
-      <c r="J50" s="62">
+      <c r="J50" s="61">
         <v>21</v>
       </c>
       <c r="K50" s="9">
@@ -4364,7 +4358,7 @@
       </c>
       <c r="M50" s="22"/>
       <c r="N50" s="10"/>
-      <c r="O50" s="56"/>
+      <c r="O50" s="55"/>
       <c r="P50" s="14"/>
       <c r="Q50" s="20"/>
       <c r="R50" s="20"/>
@@ -4395,7 +4389,7 @@
       <c r="I51" s="21">
         <v>3936.94</v>
       </c>
-      <c r="J51" s="62">
+      <c r="J51" s="61">
         <v>16</v>
       </c>
       <c r="K51" s="9">
@@ -4406,7 +4400,7 @@
       </c>
       <c r="M51" s="22"/>
       <c r="N51" s="10"/>
-      <c r="O51" s="56"/>
+      <c r="O51" s="55"/>
       <c r="P51" s="14"/>
       <c r="Q51" s="20"/>
       <c r="R51" s="20"/>
@@ -4437,7 +4431,7 @@
       <c r="I52" s="21">
         <v>5148.13</v>
       </c>
-      <c r="J52" s="62">
+      <c r="J52" s="61">
         <v>22</v>
       </c>
       <c r="K52" s="9">
@@ -4448,7 +4442,7 @@
       </c>
       <c r="M52" s="22"/>
       <c r="N52" s="10"/>
-      <c r="O52" s="56"/>
+      <c r="O52" s="55"/>
       <c r="P52" s="14"/>
       <c r="Q52" s="20"/>
       <c r="R52" s="20"/>
@@ -4479,7 +4473,7 @@
       <c r="I53" s="21">
         <v>4040.22</v>
       </c>
-      <c r="J53" s="62">
+      <c r="J53" s="61">
         <v>20</v>
       </c>
       <c r="K53" s="9">
@@ -4490,7 +4484,7 @@
       </c>
       <c r="M53" s="22"/>
       <c r="N53" s="10"/>
-      <c r="O53" s="56"/>
+      <c r="O53" s="55"/>
       <c r="P53" s="14"/>
       <c r="Q53" s="20"/>
       <c r="R53" s="20"/>
@@ -4521,7 +4515,7 @@
       <c r="I54" s="21">
         <v>3476.69</v>
       </c>
-      <c r="J54" s="62">
+      <c r="J54" s="61">
         <v>17</v>
       </c>
       <c r="K54" s="9">
@@ -4532,7 +4526,7 @@
       </c>
       <c r="M54" s="22"/>
       <c r="N54" s="10"/>
-      <c r="O54" s="56"/>
+      <c r="O54" s="55"/>
       <c r="P54" s="14"/>
       <c r="Q54" s="20"/>
       <c r="R54" s="20"/>
@@ -4563,7 +4557,7 @@
       <c r="I55" s="21">
         <v>19338.12</v>
       </c>
-      <c r="J55" s="62">
+      <c r="J55" s="61">
         <v>21</v>
       </c>
       <c r="K55" s="9">
@@ -4574,7 +4568,7 @@
       </c>
       <c r="M55" s="22"/>
       <c r="N55" s="10"/>
-      <c r="O55" s="56"/>
+      <c r="O55" s="55"/>
       <c r="P55" s="14"/>
       <c r="Q55" s="20"/>
       <c r="R55" s="20"/>
@@ -4605,7 +4599,7 @@
       <c r="I56" s="21">
         <v>5882.61</v>
       </c>
-      <c r="J56" s="62">
+      <c r="J56" s="61">
         <v>21</v>
       </c>
       <c r="K56" s="9">
@@ -4616,7 +4610,7 @@
       </c>
       <c r="M56" s="22"/>
       <c r="N56" s="10"/>
-      <c r="O56" s="56"/>
+      <c r="O56" s="55"/>
       <c r="P56" s="14"/>
       <c r="Q56" s="20"/>
       <c r="R56" s="20"/>
@@ -4647,7 +4641,7 @@
       <c r="I57" s="21">
         <v>7405.7300000000005</v>
       </c>
-      <c r="J57" s="62">
+      <c r="J57" s="61">
         <v>26</v>
       </c>
       <c r="K57" s="9">
@@ -4658,7 +4652,7 @@
       </c>
       <c r="M57" s="22"/>
       <c r="N57" s="10"/>
-      <c r="O57" s="56"/>
+      <c r="O57" s="55"/>
       <c r="P57" s="14"/>
       <c r="Q57" s="20"/>
       <c r="R57" s="20"/>
@@ -4689,7 +4683,7 @@
       <c r="I58" s="21">
         <v>2894.37</v>
       </c>
-      <c r="J58" s="62">
+      <c r="J58" s="61">
         <v>14</v>
       </c>
       <c r="K58" s="9">
@@ -4700,7 +4694,7 @@
       </c>
       <c r="M58" s="22"/>
       <c r="N58" s="10"/>
-      <c r="O58" s="56"/>
+      <c r="O58" s="55"/>
       <c r="P58" s="14"/>
       <c r="Q58" s="20"/>
       <c r="R58" s="20"/>
@@ -4731,7 +4725,7 @@
       <c r="I59" s="21">
         <v>4995.0600000000004</v>
       </c>
-      <c r="J59" s="62">
+      <c r="J59" s="61">
         <v>22</v>
       </c>
       <c r="K59" s="9">
@@ -4742,7 +4736,7 @@
       </c>
       <c r="M59" s="22"/>
       <c r="N59" s="10"/>
-      <c r="O59" s="56"/>
+      <c r="O59" s="55"/>
       <c r="P59" s="14"/>
       <c r="Q59" s="20"/>
       <c r="R59" s="20"/>
@@ -4773,7 +4767,7 @@
       <c r="I60" s="21">
         <v>3769.2599999999998</v>
       </c>
-      <c r="J60" s="62">
+      <c r="J60" s="61">
         <v>18</v>
       </c>
       <c r="K60" s="9">
@@ -4784,7 +4778,7 @@
       </c>
       <c r="M60" s="22"/>
       <c r="N60" s="10"/>
-      <c r="O60" s="56"/>
+      <c r="O60" s="55"/>
       <c r="P60" s="14"/>
       <c r="Q60" s="20"/>
       <c r="R60" s="20"/>
@@ -4815,7 +4809,7 @@
       <c r="I61" s="21">
         <v>11610.06</v>
       </c>
-      <c r="J61" s="62">
+      <c r="J61" s="61">
         <v>18</v>
       </c>
       <c r="K61" s="9">
@@ -4826,7 +4820,7 @@
       </c>
       <c r="M61" s="22"/>
       <c r="N61" s="10"/>
-      <c r="O61" s="56"/>
+      <c r="O61" s="55"/>
       <c r="P61" s="14"/>
       <c r="Q61" s="20"/>
       <c r="R61" s="20"/>
@@ -4857,7 +4851,7 @@
       <c r="I62" s="21">
         <v>3417.1000000000004</v>
       </c>
-      <c r="J62" s="62">
+      <c r="J62" s="61">
         <v>17</v>
       </c>
       <c r="K62" s="9">
@@ -4868,7 +4862,7 @@
       </c>
       <c r="M62" s="22"/>
       <c r="N62" s="10"/>
-      <c r="O62" s="56"/>
+      <c r="O62" s="55"/>
       <c r="P62" s="14"/>
       <c r="Q62" s="20"/>
       <c r="R62" s="20"/>
@@ -4899,7 +4893,7 @@
       <c r="I63" s="21">
         <v>6124.47</v>
       </c>
-      <c r="J63" s="62">
+      <c r="J63" s="61">
         <v>17</v>
       </c>
       <c r="K63" s="9">
@@ -4910,7 +4904,7 @@
       </c>
       <c r="M63" s="22"/>
       <c r="N63" s="10"/>
-      <c r="O63" s="56"/>
+      <c r="O63" s="55"/>
       <c r="P63" s="14"/>
       <c r="Q63" s="20"/>
       <c r="R63" s="20"/>
@@ -4941,7 +4935,7 @@
       <c r="I64" s="21">
         <v>4822.1499999999996</v>
       </c>
-      <c r="J64" s="62">
+      <c r="J64" s="61">
         <v>14</v>
       </c>
       <c r="K64" s="9">
@@ -4952,7 +4946,7 @@
       </c>
       <c r="M64" s="22"/>
       <c r="N64" s="10"/>
-      <c r="O64" s="56"/>
+      <c r="O64" s="55"/>
       <c r="P64" s="14"/>
       <c r="Q64" s="20"/>
       <c r="R64" s="20"/>
@@ -4983,7 +4977,7 @@
       <c r="I65" s="21">
         <v>4191.84</v>
       </c>
-      <c r="J65" s="62">
+      <c r="J65" s="61">
         <v>19</v>
       </c>
       <c r="K65" s="9">
@@ -4994,7 +4988,7 @@
       </c>
       <c r="M65" s="22"/>
       <c r="N65" s="10"/>
-      <c r="O65" s="56"/>
+      <c r="O65" s="55"/>
       <c r="P65" s="14"/>
       <c r="Q65" s="20"/>
       <c r="R65" s="20"/>
@@ -5025,7 +5019,7 @@
       <c r="I66" s="21">
         <v>7290.81</v>
       </c>
-      <c r="J66" s="62">
+      <c r="J66" s="61">
         <v>21</v>
       </c>
       <c r="K66" s="9">
@@ -5036,7 +5030,7 @@
       </c>
       <c r="M66" s="22"/>
       <c r="N66" s="10"/>
-      <c r="O66" s="56"/>
+      <c r="O66" s="55"/>
       <c r="P66" s="14"/>
       <c r="Q66" s="20"/>
       <c r="R66" s="20"/>
@@ -5067,7 +5061,7 @@
       <c r="I67" s="21">
         <v>5914.39</v>
       </c>
-      <c r="J67" s="62">
+      <c r="J67" s="61">
         <v>18</v>
       </c>
       <c r="K67" s="9">
@@ -5078,7 +5072,7 @@
       </c>
       <c r="M67" s="22"/>
       <c r="N67" s="10"/>
-      <c r="O67" s="56"/>
+      <c r="O67" s="55"/>
       <c r="P67" s="14"/>
       <c r="Q67" s="20"/>
       <c r="R67" s="20"/>
@@ -5109,7 +5103,7 @@
       <c r="I68" s="21">
         <v>4633.6500000000005</v>
       </c>
-      <c r="J68" s="62">
+      <c r="J68" s="61">
         <v>15</v>
       </c>
       <c r="K68" s="9">
@@ -5120,7 +5114,7 @@
       </c>
       <c r="M68" s="22"/>
       <c r="N68" s="10"/>
-      <c r="O68" s="56"/>
+      <c r="O68" s="55"/>
       <c r="P68" s="14"/>
       <c r="Q68" s="20"/>
       <c r="R68" s="20"/>
@@ -5151,7 +5145,7 @@
       <c r="I69" s="21">
         <v>17887.07</v>
       </c>
-      <c r="J69" s="62">
+      <c r="J69" s="61">
         <v>26</v>
       </c>
       <c r="K69" s="9">
@@ -5162,7 +5156,7 @@
       </c>
       <c r="M69" s="22"/>
       <c r="N69" s="10"/>
-      <c r="O69" s="56"/>
+      <c r="O69" s="55"/>
       <c r="P69" s="14"/>
       <c r="Q69" s="20"/>
       <c r="R69" s="20"/>
@@ -5197,7 +5191,7 @@
       <c r="I70" s="21">
         <v>2434.52</v>
       </c>
-      <c r="J70" s="62">
+      <c r="J70" s="61">
         <v>8</v>
       </c>
       <c r="K70" s="9">
@@ -5208,14 +5202,14 @@
       </c>
       <c r="M70" s="22"/>
       <c r="N70" s="10"/>
-      <c r="O70" s="56"/>
+      <c r="O70" s="55"/>
       <c r="P70" s="14"/>
       <c r="Q70" s="20"/>
       <c r="R70" s="20"/>
       <c r="S70" s="20"/>
       <c r="T70" s="20"/>
       <c r="U70" s="20"/>
-      <c r="V70" s="130">
+      <c r="V70" s="129">
         <v>483.37583283000004</v>
       </c>
     </row>
@@ -5245,7 +5239,7 @@
       <c r="I71" s="21">
         <v>8962</v>
       </c>
-      <c r="J71" s="62">
+      <c r="J71" s="61">
         <v>12</v>
       </c>
       <c r="K71" s="9">
@@ -5256,26 +5250,26 @@
       </c>
       <c r="M71" s="22"/>
       <c r="N71" s="10"/>
-      <c r="O71" s="56"/>
-      <c r="P71" s="127">
+      <c r="O71" s="55"/>
+      <c r="P71" s="126">
         <v>10</v>
       </c>
-      <c r="Q71" s="128">
-        <v>0</v>
-      </c>
-      <c r="R71" s="128">
+      <c r="Q71" s="127">
+        <v>0</v>
+      </c>
+      <c r="R71" s="127">
         <v>373.43695490000005</v>
       </c>
-      <c r="S71" s="128">
-        <v>0</v>
-      </c>
-      <c r="T71" s="128">
-        <v>0</v>
-      </c>
-      <c r="U71" s="129">
-        <v>0</v>
-      </c>
-      <c r="V71" s="131">
+      <c r="S71" s="127">
+        <v>0</v>
+      </c>
+      <c r="T71" s="127">
+        <v>0</v>
+      </c>
+      <c r="U71" s="128">
+        <v>0</v>
+      </c>
+      <c r="V71" s="130">
         <v>383.43695489999999</v>
       </c>
     </row>
@@ -5305,7 +5299,7 @@
       <c r="I72" s="21">
         <v>4383</v>
       </c>
-      <c r="J72" s="62">
+      <c r="J72" s="61">
         <v>11</v>
       </c>
       <c r="K72" s="9">
@@ -5316,7 +5310,7 @@
       </c>
       <c r="M72" s="22"/>
       <c r="N72" s="10"/>
-      <c r="O72" s="56"/>
+      <c r="O72" s="55"/>
       <c r="P72" s="43">
         <v>41.204999999999998</v>
       </c>
@@ -5335,7 +5329,7 @@
       <c r="U72" s="45">
         <v>0</v>
       </c>
-      <c r="V72" s="131">
+      <c r="V72" s="130">
         <v>498.78207258000003</v>
       </c>
     </row>
@@ -5365,7 +5359,7 @@
       <c r="I73" s="21">
         <v>18429</v>
       </c>
-      <c r="J73" s="62">
+      <c r="J73" s="61">
         <v>19</v>
       </c>
       <c r="K73" s="9">
@@ -5376,7 +5370,7 @@
       </c>
       <c r="M73" s="22"/>
       <c r="N73" s="10"/>
-      <c r="O73" s="56"/>
+      <c r="O73" s="55"/>
       <c r="P73" s="43">
         <v>133.23450000000003</v>
       </c>
@@ -5395,7 +5389,7 @@
       <c r="U73" s="45">
         <v>0</v>
       </c>
-      <c r="V73" s="131">
+      <c r="V73" s="130">
         <v>690.73018245000003</v>
       </c>
     </row>
@@ -5425,7 +5419,7 @@
       <c r="I74" s="21">
         <v>4572</v>
       </c>
-      <c r="J74" s="62">
+      <c r="J74" s="61">
         <v>16</v>
       </c>
       <c r="K74" s="9">
@@ -5436,7 +5430,7 @@
       </c>
       <c r="M74" s="22"/>
       <c r="N74" s="10"/>
-      <c r="O74" s="56"/>
+      <c r="O74" s="55"/>
       <c r="P74" s="43">
         <v>17.557105</v>
       </c>
@@ -5455,7 +5449,7 @@
       <c r="U74" s="45">
         <v>0</v>
       </c>
-      <c r="V74" s="131">
+      <c r="V74" s="130">
         <v>611.81162099999995</v>
       </c>
     </row>
@@ -5485,7 +5479,7 @@
       <c r="I75" s="21">
         <v>5484</v>
       </c>
-      <c r="J75" s="62">
+      <c r="J75" s="61">
         <v>20</v>
       </c>
       <c r="K75" s="9">
@@ -5496,7 +5490,7 @@
       </c>
       <c r="M75" s="22"/>
       <c r="N75" s="10"/>
-      <c r="O75" s="56"/>
+      <c r="O75" s="55"/>
       <c r="P75" s="43">
         <v>0</v>
       </c>
@@ -5515,7 +5509,7 @@
       <c r="U75" s="45">
         <v>0</v>
       </c>
-      <c r="V75" s="131">
+      <c r="V75" s="130">
         <v>1039.36205819</v>
       </c>
     </row>
@@ -5545,7 +5539,7 @@
       <c r="I76" s="21">
         <v>7957</v>
       </c>
-      <c r="J76" s="62">
+      <c r="J76" s="61">
         <v>20</v>
       </c>
       <c r="K76" s="9">
@@ -5556,7 +5550,7 @@
       </c>
       <c r="M76" s="22"/>
       <c r="N76" s="10"/>
-      <c r="O76" s="56"/>
+      <c r="O76" s="55"/>
       <c r="P76" s="43">
         <v>70</v>
       </c>
@@ -5575,7 +5569,7 @@
       <c r="U76" s="45">
         <v>0</v>
       </c>
-      <c r="V76" s="131">
+      <c r="V76" s="130">
         <v>1075.1466929999999</v>
       </c>
     </row>
@@ -5605,7 +5599,7 @@
       <c r="I77" s="21">
         <v>4751</v>
       </c>
-      <c r="J77" s="62">
+      <c r="J77" s="61">
         <v>17</v>
       </c>
       <c r="K77" s="9">
@@ -5616,7 +5610,7 @@
       </c>
       <c r="M77" s="22"/>
       <c r="N77" s="10"/>
-      <c r="O77" s="56"/>
+      <c r="O77" s="55"/>
       <c r="P77" s="43">
         <v>180.78066790600002</v>
       </c>
@@ -5635,7 +5629,7 @@
       <c r="U77" s="45">
         <v>0</v>
       </c>
-      <c r="V77" s="131">
+      <c r="V77" s="130">
         <v>1120.6751705659999</v>
       </c>
     </row>
@@ -5665,7 +5659,7 @@
       <c r="I78" s="21">
         <v>9377</v>
       </c>
-      <c r="J78" s="62">
+      <c r="J78" s="61">
         <v>17</v>
       </c>
       <c r="K78" s="9">
@@ -5676,7 +5670,7 @@
       </c>
       <c r="M78" s="22"/>
       <c r="N78" s="10"/>
-      <c r="O78" s="56"/>
+      <c r="O78" s="55"/>
       <c r="P78" s="43">
         <v>192.77777699999999</v>
       </c>
@@ -5695,7 +5689,7 @@
       <c r="U78" s="45">
         <v>0</v>
       </c>
-      <c r="V78" s="131">
+      <c r="V78" s="130">
         <v>2340.9843438099997</v>
       </c>
     </row>
@@ -5725,7 +5719,7 @@
       <c r="I79" s="21">
         <v>9639</v>
       </c>
-      <c r="J79" s="62">
+      <c r="J79" s="61">
         <v>18</v>
       </c>
       <c r="K79" s="9">
@@ -5736,7 +5730,7 @@
       </c>
       <c r="M79" s="22"/>
       <c r="N79" s="10"/>
-      <c r="O79" s="56"/>
+      <c r="O79" s="55"/>
       <c r="P79" s="43">
         <v>12</v>
       </c>
@@ -5755,7 +5749,7 @@
       <c r="U79" s="45">
         <v>0</v>
       </c>
-      <c r="V79" s="131">
+      <c r="V79" s="130">
         <v>1341.8820957600001</v>
       </c>
     </row>
@@ -5785,7 +5779,7 @@
       <c r="I80" s="21">
         <v>15739</v>
       </c>
-      <c r="J80" s="62">
+      <c r="J80" s="61">
         <v>22</v>
       </c>
       <c r="K80" s="9">
@@ -5796,7 +5790,7 @@
       </c>
       <c r="M80" s="22"/>
       <c r="N80" s="10"/>
-      <c r="O80" s="56"/>
+      <c r="O80" s="55"/>
       <c r="P80" s="43">
         <v>15</v>
       </c>
@@ -5815,7 +5809,7 @@
       <c r="U80" s="45">
         <v>0</v>
       </c>
-      <c r="V80" s="131">
+      <c r="V80" s="130">
         <v>897.90784900000006</v>
       </c>
     </row>
@@ -5845,7 +5839,7 @@
       <c r="I81" s="21">
         <v>9721</v>
       </c>
-      <c r="J81" s="62">
+      <c r="J81" s="61">
         <v>20</v>
       </c>
       <c r="K81" s="9">
@@ -5856,7 +5850,7 @@
       </c>
       <c r="M81" s="22"/>
       <c r="N81" s="10"/>
-      <c r="O81" s="56"/>
+      <c r="O81" s="55"/>
       <c r="P81" s="43">
         <v>67.461529999999996</v>
       </c>
@@ -5875,7 +5869,7 @@
       <c r="U81" s="45">
         <v>0</v>
       </c>
-      <c r="V81" s="131">
+      <c r="V81" s="130">
         <v>976.96602299999995</v>
       </c>
     </row>
@@ -5906,7 +5900,7 @@
       <c r="I82" s="21">
         <v>5904</v>
       </c>
-      <c r="J82" s="62">
+      <c r="J82" s="61">
         <v>16</v>
       </c>
       <c r="K82" s="9">
@@ -5917,7 +5911,7 @@
       </c>
       <c r="M82" s="22"/>
       <c r="N82" s="10"/>
-      <c r="O82" s="56"/>
+      <c r="O82" s="55"/>
       <c r="P82" s="43">
         <v>0</v>
       </c>
@@ -5936,7 +5930,7 @@
       <c r="U82" s="45">
         <v>0</v>
       </c>
-      <c r="V82" s="131">
+      <c r="V82" s="130">
         <v>594.96512578000033</v>
       </c>
     </row>
@@ -5967,7 +5961,7 @@
       <c r="I83" s="21">
         <v>5772</v>
       </c>
-      <c r="J83" s="62">
+      <c r="J83" s="61">
         <v>16</v>
       </c>
       <c r="K83" s="9">
@@ -5978,7 +5972,7 @@
       </c>
       <c r="M83" s="22"/>
       <c r="N83" s="15"/>
-      <c r="O83" s="57"/>
+      <c r="O83" s="56"/>
       <c r="P83" s="43">
         <v>100</v>
       </c>
@@ -5997,7 +5991,7 @@
       <c r="U83" s="45">
         <v>0</v>
       </c>
-      <c r="V83" s="131">
+      <c r="V83" s="130">
         <v>719.61598692999894</v>
       </c>
     </row>
@@ -6028,7 +6022,7 @@
       <c r="I84" s="21">
         <v>26370</v>
       </c>
-      <c r="J84" s="62">
+      <c r="J84" s="61">
         <v>15</v>
       </c>
       <c r="K84" s="9">
@@ -6039,7 +6033,7 @@
       </c>
       <c r="M84" s="22"/>
       <c r="N84" s="15"/>
-      <c r="O84" s="58">
+      <c r="O84" s="57">
         <v>7.75</v>
       </c>
       <c r="P84" s="43">
@@ -6060,7 +6054,7 @@
       <c r="U84" s="45">
         <v>0</v>
       </c>
-      <c r="V84" s="131">
+      <c r="V84" s="130">
         <v>1724.7166384699958</v>
       </c>
     </row>
@@ -6091,7 +6085,7 @@
       <c r="I85" s="21">
         <v>7544</v>
       </c>
-      <c r="J85" s="62">
+      <c r="J85" s="61">
         <v>25</v>
       </c>
       <c r="K85" s="9">
@@ -6102,7 +6096,7 @@
       </c>
       <c r="M85" s="22"/>
       <c r="N85" s="15"/>
-      <c r="O85" s="59">
+      <c r="O85" s="58">
         <v>2</v>
       </c>
       <c r="P85" s="43">
@@ -6123,7 +6117,7 @@
       <c r="U85" s="45">
         <v>0</v>
       </c>
-      <c r="V85" s="131">
+      <c r="V85" s="130">
         <v>1836.7390234499983</v>
       </c>
     </row>
@@ -6154,7 +6148,7 @@
       <c r="I86" s="21">
         <v>13809</v>
       </c>
-      <c r="J86" s="62">
+      <c r="J86" s="61">
         <v>18</v>
       </c>
       <c r="K86" s="9">
@@ -6167,7 +6161,7 @@
       <c r="N86" s="16">
         <v>20.9</v>
       </c>
-      <c r="O86" s="59">
+      <c r="O86" s="58">
         <v>3.75</v>
       </c>
       <c r="P86" s="43">
@@ -6188,7 +6182,7 @@
       <c r="U86" s="45">
         <v>0</v>
       </c>
-      <c r="V86" s="131">
+      <c r="V86" s="130">
         <v>2237.8985550599996</v>
       </c>
     </row>
@@ -6219,7 +6213,7 @@
       <c r="I87" s="21">
         <v>31141</v>
       </c>
-      <c r="J87" s="62">
+      <c r="J87" s="61">
         <v>18</v>
       </c>
       <c r="K87" s="9">
@@ -6232,7 +6226,7 @@
       <c r="N87" s="17">
         <v>22.1</v>
       </c>
-      <c r="O87" s="59">
+      <c r="O87" s="58">
         <v>4.9718074927474962</v>
       </c>
       <c r="P87" s="43">
@@ -6253,7 +6247,7 @@
       <c r="U87" s="45">
         <v>0</v>
       </c>
-      <c r="V87" s="131">
+      <c r="V87" s="130">
         <v>1863.781022732996</v>
       </c>
     </row>
@@ -6284,7 +6278,7 @@
       <c r="I88" s="21">
         <v>24941</v>
       </c>
-      <c r="J88" s="62">
+      <c r="J88" s="61">
         <v>21</v>
       </c>
       <c r="K88" s="9">
@@ -6297,7 +6291,7 @@
       <c r="N88" s="17">
         <v>26.4</v>
       </c>
-      <c r="O88" s="59">
+      <c r="O88" s="58">
         <v>8.0241472930920423</v>
       </c>
       <c r="P88" s="43">
@@ -6318,7 +6312,7 @@
       <c r="U88" s="45">
         <v>0</v>
       </c>
-      <c r="V88" s="131">
+      <c r="V88" s="130">
         <v>1915.751794728611</v>
       </c>
     </row>
@@ -6349,7 +6343,7 @@
       <c r="I89" s="21">
         <v>15635</v>
       </c>
-      <c r="J89" s="62">
+      <c r="J89" s="61">
         <v>18</v>
       </c>
       <c r="K89" s="9">
@@ -6362,7 +6356,7 @@
       <c r="N89" s="17">
         <v>25.4</v>
       </c>
-      <c r="O89" s="59">
+      <c r="O89" s="58">
         <v>6.903614457831325</v>
       </c>
       <c r="P89" s="43">
@@ -6383,7 +6377,7 @@
       <c r="U89" s="45">
         <v>0</v>
       </c>
-      <c r="V89" s="131">
+      <c r="V89" s="130">
         <v>1822.2257044100006</v>
       </c>
     </row>
@@ -6414,7 +6408,7 @@
       <c r="I90" s="21">
         <v>16760</v>
       </c>
-      <c r="J90" s="62">
+      <c r="J90" s="61">
         <v>17</v>
       </c>
       <c r="K90" s="9">
@@ -6427,7 +6421,7 @@
       <c r="N90" s="17">
         <v>21.1</v>
       </c>
-      <c r="O90" s="59">
+      <c r="O90" s="58">
         <v>7.5023159451917243</v>
       </c>
       <c r="P90" s="43">
@@ -6448,7 +6442,7 @@
       <c r="U90" s="45">
         <v>0</v>
       </c>
-      <c r="V90" s="131">
+      <c r="V90" s="130">
         <v>2090.0519868203842</v>
       </c>
     </row>
@@ -6479,7 +6473,7 @@
       <c r="I91" s="21">
         <v>15794</v>
       </c>
-      <c r="J91" s="62">
+      <c r="J91" s="61">
         <v>15</v>
       </c>
       <c r="K91" s="9">
@@ -6492,7 +6486,7 @@
       <c r="N91" s="17">
         <v>25.8</v>
       </c>
-      <c r="O91" s="59">
+      <c r="O91" s="58">
         <v>7.1675977653631291</v>
       </c>
       <c r="P91" s="43">
@@ -6513,7 +6507,7 @@
       <c r="U91" s="45">
         <v>0</v>
       </c>
-      <c r="V91" s="131">
+      <c r="V91" s="130">
         <v>1289.31642437</v>
       </c>
     </row>
@@ -6544,7 +6538,7 @@
       <c r="I92" s="21">
         <v>20122</v>
       </c>
-      <c r="J92" s="62">
+      <c r="J92" s="61">
         <v>14</v>
       </c>
       <c r="K92" s="9">
@@ -6557,7 +6551,7 @@
       <c r="N92" s="17">
         <v>25.4</v>
       </c>
-      <c r="O92" s="59">
+      <c r="O92" s="58">
         <v>7.7307163681799258</v>
       </c>
       <c r="P92" s="43">
@@ -6578,7 +6572,7 @@
       <c r="U92" s="45">
         <v>0</v>
       </c>
-      <c r="V92" s="131">
+      <c r="V92" s="130">
         <v>1368.2420682264003</v>
       </c>
     </row>
@@ -6609,7 +6603,7 @@
       <c r="I93" s="21">
         <v>10900</v>
       </c>
-      <c r="J93" s="62">
+      <c r="J93" s="61">
         <v>23</v>
       </c>
       <c r="K93" s="9">
@@ -6622,7 +6616,7 @@
       <c r="N93" s="17">
         <v>25.4</v>
       </c>
-      <c r="O93" s="59">
+      <c r="O93" s="58">
         <v>6.9894113551494916</v>
       </c>
       <c r="P93" s="43">
@@ -6643,7 +6637,7 @@
       <c r="U93" s="45">
         <v>0</v>
       </c>
-      <c r="V93" s="131">
+      <c r="V93" s="130">
         <v>2207.7998523933511</v>
       </c>
     </row>
@@ -6674,7 +6668,7 @@
       <c r="I94" s="21">
         <v>34586</v>
       </c>
-      <c r="J94" s="62">
+      <c r="J94" s="61">
         <v>17</v>
       </c>
       <c r="K94" s="9">
@@ -6687,7 +6681,7 @@
       <c r="N94" s="17">
         <v>25</v>
       </c>
-      <c r="O94" s="59">
+      <c r="O94" s="58">
         <v>7.0940139874958286</v>
       </c>
       <c r="P94" s="43">
@@ -6708,7 +6702,7 @@
       <c r="U94" s="45">
         <v>0</v>
       </c>
-      <c r="V94" s="131">
+      <c r="V94" s="130">
         <v>1455.4871785988357</v>
       </c>
     </row>
@@ -6739,7 +6733,7 @@
       <c r="I95" s="21">
         <v>16874</v>
       </c>
-      <c r="J95" s="62">
+      <c r="J95" s="61">
         <v>12</v>
       </c>
       <c r="K95" s="9">
@@ -6752,7 +6746,7 @@
       <c r="N95" s="17">
         <v>22.6</v>
       </c>
-      <c r="O95" s="59">
+      <c r="O95" s="58">
         <v>6.8868760244985729</v>
       </c>
       <c r="P95" s="43">
@@ -6773,7 +6767,7 @@
       <c r="U95" s="45">
         <v>0</v>
       </c>
-      <c r="V95" s="131">
+      <c r="V95" s="130">
         <v>1201.4806110607515</v>
       </c>
     </row>
@@ -6804,7 +6798,7 @@
       <c r="I96" s="21">
         <v>14020</v>
       </c>
-      <c r="J96" s="62">
+      <c r="J96" s="61">
         <v>17</v>
       </c>
       <c r="K96" s="9">
@@ -6817,7 +6811,7 @@
       <c r="N96" s="17">
         <v>20</v>
       </c>
-      <c r="O96" s="59">
+      <c r="O96" s="58">
         <v>6.6784985946894153</v>
       </c>
       <c r="P96" s="43">
@@ -6838,7 +6832,7 @@
       <c r="U96" s="45">
         <v>0</v>
       </c>
-      <c r="V96" s="131">
+      <c r="V96" s="130">
         <v>2007.4692817746029</v>
       </c>
     </row>
@@ -6869,7 +6863,7 @@
       <c r="I97" s="21">
         <v>13638</v>
       </c>
-      <c r="J97" s="62">
+      <c r="J97" s="61">
         <v>16</v>
       </c>
       <c r="K97" s="9">
@@ -6882,7 +6876,7 @@
       <c r="N97" s="17">
         <v>22.5</v>
       </c>
-      <c r="O97" s="59">
+      <c r="O97" s="58">
         <v>6.7934761806792272</v>
       </c>
       <c r="P97" s="43">
@@ -6903,7 +6897,7 @@
       <c r="U97" s="45">
         <v>0</v>
       </c>
-      <c r="V97" s="131">
+      <c r="V97" s="130">
         <v>1962.7879201480189</v>
       </c>
     </row>
@@ -6934,7 +6928,7 @@
       <c r="I98" s="21">
         <v>28565</v>
       </c>
-      <c r="J98" s="62">
+      <c r="J98" s="61">
         <v>19</v>
       </c>
       <c r="K98" s="9">
@@ -6947,7 +6941,7 @@
       <c r="N98" s="17">
         <v>23.6</v>
       </c>
-      <c r="O98" s="59">
+      <c r="O98" s="58">
         <v>6.3490128159204611</v>
       </c>
       <c r="P98" s="43">
@@ -6968,7 +6962,7 @@
       <c r="U98" s="45">
         <v>0</v>
       </c>
-      <c r="V98" s="131">
+      <c r="V98" s="130">
         <v>2077.0808681895724</v>
       </c>
     </row>
@@ -6999,7 +6993,7 @@
       <c r="I99" s="21">
         <v>24151</v>
       </c>
-      <c r="J99" s="62">
+      <c r="J99" s="61">
         <v>17</v>
       </c>
       <c r="K99" s="9">
@@ -7012,7 +7006,7 @@
       <c r="N99" s="17">
         <v>22.7</v>
       </c>
-      <c r="O99" s="59">
+      <c r="O99" s="58">
         <v>6.2488768742165952</v>
       </c>
       <c r="P99" s="43">
@@ -7033,7 +7027,7 @@
       <c r="U99" s="45">
         <v>0</v>
       </c>
-      <c r="V99" s="131">
+      <c r="V99" s="130">
         <v>2355.6036568854156</v>
       </c>
     </row>
@@ -7064,7 +7058,7 @@
       <c r="I100" s="21">
         <v>33199</v>
       </c>
-      <c r="J100" s="62">
+      <c r="J100" s="61">
         <v>19</v>
       </c>
       <c r="K100" s="9">
@@ -7077,7 +7071,7 @@
       <c r="N100" s="17">
         <v>26</v>
       </c>
-      <c r="O100" s="59">
+      <c r="O100" s="58">
         <v>7.0148224375198964</v>
       </c>
       <c r="P100" s="43">
@@ -7098,7 +7092,7 @@
       <c r="U100" s="45">
         <v>0</v>
       </c>
-      <c r="V100" s="131">
+      <c r="V100" s="130">
         <v>2450.4227428267309</v>
       </c>
     </row>
@@ -7129,7 +7123,7 @@
       <c r="I101" s="21">
         <v>12071</v>
       </c>
-      <c r="J101" s="62">
+      <c r="J101" s="61">
         <v>22</v>
       </c>
       <c r="K101" s="9">
@@ -7142,7 +7136,7 @@
       <c r="N101" s="17">
         <v>27.2</v>
       </c>
-      <c r="O101" s="59">
+      <c r="O101" s="58">
         <v>7.8775242960064329</v>
       </c>
       <c r="P101" s="43">
@@ -7163,7 +7157,7 @@
       <c r="U101" s="45">
         <v>0</v>
       </c>
-      <c r="V101" s="131">
+      <c r="V101" s="130">
         <v>2356.8365575739444</v>
       </c>
     </row>
@@ -7194,7 +7188,7 @@
       <c r="I102" s="21">
         <v>29045</v>
       </c>
-      <c r="J102" s="62">
+      <c r="J102" s="61">
         <v>23</v>
       </c>
       <c r="K102" s="9">
@@ -7207,7 +7201,7 @@
       <c r="N102" s="17">
         <v>28.2</v>
       </c>
-      <c r="O102" s="59">
+      <c r="O102" s="58">
         <v>7.8988699995765508</v>
       </c>
       <c r="P102" s="43">
@@ -7228,7 +7222,7 @@
       <c r="U102" s="45">
         <v>0</v>
       </c>
-      <c r="V102" s="131">
+      <c r="V102" s="130">
         <v>2453.1386800653099</v>
       </c>
     </row>
@@ -7259,7 +7253,7 @@
       <c r="I103" s="21">
         <v>26475</v>
       </c>
-      <c r="J103" s="62">
+      <c r="J103" s="61">
         <v>14</v>
       </c>
       <c r="K103" s="9">
@@ -7272,7 +7266,7 @@
       <c r="N103" s="17">
         <v>28.4</v>
       </c>
-      <c r="O103" s="59">
+      <c r="O103" s="58">
         <v>7.8</v>
       </c>
       <c r="P103" s="43">
@@ -7293,7 +7287,7 @@
       <c r="U103" s="45">
         <v>0</v>
       </c>
-      <c r="V103" s="131">
+      <c r="V103" s="130">
         <v>1854.1296044345042</v>
       </c>
     </row>
@@ -7324,7 +7318,7 @@
       <c r="I104" s="21">
         <v>18861</v>
       </c>
-      <c r="J104" s="62">
+      <c r="J104" s="61">
         <v>15</v>
       </c>
       <c r="K104" s="9">
@@ -7337,7 +7331,7 @@
       <c r="N104" s="17">
         <v>30.5</v>
       </c>
-      <c r="O104" s="59">
+      <c r="O104" s="58">
         <v>8.4</v>
       </c>
       <c r="P104" s="43">
@@ -7358,7 +7352,7 @@
       <c r="U104" s="45">
         <v>0</v>
       </c>
-      <c r="V104" s="131">
+      <c r="V104" s="130">
         <v>2137.3602617755191</v>
       </c>
     </row>
@@ -7389,7 +7383,7 @@
       <c r="I105" s="21">
         <v>47107</v>
       </c>
-      <c r="J105" s="62">
+      <c r="J105" s="61">
         <v>24</v>
       </c>
       <c r="K105" s="9">
@@ -7402,7 +7396,7 @@
       <c r="N105" s="17">
         <v>29.9</v>
       </c>
-      <c r="O105" s="59">
+      <c r="O105" s="58">
         <v>8.3000000000000007</v>
       </c>
       <c r="P105" s="43">
@@ -7423,7 +7417,7 @@
       <c r="U105" s="45">
         <v>0</v>
       </c>
-      <c r="V105" s="131">
+      <c r="V105" s="130">
         <v>2980.8778224858006</v>
       </c>
     </row>
@@ -7454,7 +7448,7 @@
       <c r="I106" s="21">
         <v>33081</v>
       </c>
-      <c r="J106" s="62">
+      <c r="J106" s="61">
         <v>15</v>
       </c>
       <c r="K106" s="9">
@@ -7467,7 +7461,7 @@
       <c r="N106" s="17">
         <v>27.6</v>
       </c>
-      <c r="O106" s="59">
+      <c r="O106" s="58">
         <v>8.4</v>
       </c>
       <c r="P106" s="43">
@@ -7488,7 +7482,7 @@
       <c r="U106" s="45">
         <v>0</v>
       </c>
-      <c r="V106" s="131">
+      <c r="V106" s="130">
         <v>2219.4222023167608</v>
       </c>
     </row>
@@ -7519,7 +7513,7 @@
       <c r="I107" s="21">
         <v>27009</v>
       </c>
-      <c r="J107" s="62">
+      <c r="J107" s="61">
         <v>5</v>
       </c>
       <c r="K107" s="9">
@@ -7532,7 +7526,7 @@
       <c r="N107" s="17">
         <v>28.1</v>
       </c>
-      <c r="O107" s="59">
+      <c r="O107" s="58">
         <v>8.4</v>
       </c>
       <c r="P107" s="43">
@@ -7553,7 +7547,7 @@
       <c r="U107" s="45">
         <v>0</v>
       </c>
-      <c r="V107" s="131">
+      <c r="V107" s="130">
         <v>2498.9999223975997</v>
       </c>
     </row>
@@ -7584,7 +7578,7 @@
       <c r="I108" s="21">
         <v>16890</v>
       </c>
-      <c r="J108" s="62">
+      <c r="J108" s="61">
         <v>18</v>
       </c>
       <c r="K108" s="9">
@@ -7597,7 +7591,7 @@
       <c r="N108" s="17">
         <v>27.6</v>
       </c>
-      <c r="O108" s="59">
+      <c r="O108" s="58">
         <v>8.4</v>
       </c>
       <c r="P108" s="43">
@@ -7618,7 +7612,7 @@
       <c r="U108" s="45">
         <v>0</v>
       </c>
-      <c r="V108" s="131">
+      <c r="V108" s="130">
         <v>2621.3675615030133</v>
       </c>
     </row>
@@ -7649,7 +7643,7 @@
       <c r="I109" s="21">
         <v>37209</v>
       </c>
-      <c r="J109" s="62">
+      <c r="J109" s="61">
         <v>18</v>
       </c>
       <c r="K109" s="9">
@@ -7662,7 +7656,7 @@
       <c r="N109" s="17">
         <v>28.5</v>
       </c>
-      <c r="O109" s="59">
+      <c r="O109" s="58">
         <v>8.6</v>
       </c>
       <c r="P109" s="43">
@@ -7683,7 +7677,7 @@
       <c r="U109" s="45">
         <v>0</v>
       </c>
-      <c r="V109" s="131">
+      <c r="V109" s="130">
         <v>2808.0413760642091</v>
       </c>
     </row>
@@ -7714,7 +7708,7 @@
       <c r="I110" s="21">
         <v>5732</v>
       </c>
-      <c r="J110" s="62">
+      <c r="J110" s="61">
         <v>11</v>
       </c>
       <c r="K110" s="9">
@@ -7727,7 +7721,7 @@
       <c r="N110" s="17">
         <v>35</v>
       </c>
-      <c r="O110" s="59">
+      <c r="O110" s="58">
         <v>8.7999999999999989</v>
       </c>
       <c r="P110" s="43">
@@ -7748,7 +7742,7 @@
       <c r="U110" s="45">
         <v>0</v>
       </c>
-      <c r="V110" s="131">
+      <c r="V110" s="130">
         <v>3057.9388794426554</v>
       </c>
     </row>
@@ -7779,7 +7773,7 @@
       <c r="I111" s="21">
         <v>7053</v>
       </c>
-      <c r="J111" s="62">
+      <c r="J111" s="61">
         <v>12</v>
       </c>
       <c r="K111" s="9">
@@ -7792,7 +7786,7 @@
       <c r="N111" s="17">
         <v>31.3</v>
       </c>
-      <c r="O111" s="59">
+      <c r="O111" s="58">
         <v>8.6</v>
       </c>
       <c r="P111" s="43">
@@ -7813,7 +7807,7 @@
       <c r="U111" s="45">
         <v>0</v>
       </c>
-      <c r="V111" s="131">
+      <c r="V111" s="130">
         <v>3345.4575262742351</v>
       </c>
     </row>
@@ -7844,7 +7838,7 @@
       <c r="I112" s="21">
         <v>6826</v>
       </c>
-      <c r="J112" s="62">
+      <c r="J112" s="61">
         <v>10</v>
       </c>
       <c r="K112" s="9">
@@ -7857,7 +7851,7 @@
       <c r="N112" s="17">
         <v>38.700000000000003</v>
       </c>
-      <c r="O112" s="59">
+      <c r="O112" s="58">
         <v>9.8000000000000007</v>
       </c>
       <c r="P112" s="43">
@@ -7878,7 +7872,7 @@
       <c r="U112" s="45">
         <v>0</v>
       </c>
-      <c r="V112" s="131">
+      <c r="V112" s="130">
         <v>3270.1536804432599</v>
       </c>
     </row>
@@ -7909,7 +7903,7 @@
       <c r="I113" s="21">
         <v>6452</v>
       </c>
-      <c r="J113" s="62">
+      <c r="J113" s="61">
         <v>12</v>
       </c>
       <c r="K113" s="9">
@@ -7922,7 +7916,7 @@
       <c r="N113" s="17">
         <v>40.4</v>
       </c>
-      <c r="O113" s="59">
+      <c r="O113" s="58">
         <v>9</v>
       </c>
       <c r="P113" s="43">
@@ -7943,7 +7937,7 @@
       <c r="U113" s="45">
         <v>0</v>
       </c>
-      <c r="V113" s="131">
+      <c r="V113" s="130">
         <v>3305.8174182644361</v>
       </c>
     </row>
@@ -7974,7 +7968,7 @@
       <c r="I114" s="21">
         <v>9511</v>
       </c>
-      <c r="J114" s="62">
+      <c r="J114" s="61">
         <v>13</v>
       </c>
       <c r="K114" s="9">
@@ -7987,7 +7981,7 @@
       <c r="N114" s="17">
         <v>39.299999999999997</v>
       </c>
-      <c r="O114" s="59">
+      <c r="O114" s="58">
         <v>10</v>
       </c>
       <c r="P114" s="43">
@@ -8008,7 +8002,7 @@
       <c r="U114" s="45">
         <v>0</v>
       </c>
-      <c r="V114" s="131">
+      <c r="V114" s="130">
         <v>4144.6523041640139</v>
       </c>
     </row>
@@ -8039,7 +8033,7 @@
       <c r="I115" s="21">
         <v>9008</v>
       </c>
-      <c r="J115" s="62">
+      <c r="J115" s="61">
         <v>11</v>
       </c>
       <c r="K115" s="9">
@@ -8052,7 +8046,7 @@
       <c r="N115" s="17">
         <v>46.3</v>
       </c>
-      <c r="O115" s="59">
+      <c r="O115" s="58">
         <v>11.4</v>
       </c>
       <c r="P115" s="43">
@@ -8073,7 +8067,7 @@
       <c r="U115" s="45">
         <v>0</v>
       </c>
-      <c r="V115" s="131">
+      <c r="V115" s="130">
         <v>5212.484014091784</v>
       </c>
     </row>
@@ -8104,7 +8098,7 @@
       <c r="I116" s="21">
         <v>20778</v>
       </c>
-      <c r="J116" s="62">
+      <c r="J116" s="61">
         <v>14</v>
       </c>
       <c r="K116" s="9">
@@ -8117,7 +8111,7 @@
       <c r="N116" s="17">
         <v>52.2</v>
       </c>
-      <c r="O116" s="59">
+      <c r="O116" s="58">
         <v>13.100000000000001</v>
       </c>
       <c r="P116" s="43">
@@ -8138,7 +8132,7 @@
       <c r="U116" s="45">
         <v>0</v>
       </c>
-      <c r="V116" s="131">
+      <c r="V116" s="130">
         <v>4562.4965246113043</v>
       </c>
     </row>
@@ -8169,7 +8163,7 @@
       <c r="I117" s="21">
         <v>13963</v>
       </c>
-      <c r="J117" s="62">
+      <c r="J117" s="61">
         <v>16</v>
       </c>
       <c r="K117" s="9">
@@ -8182,7 +8176,7 @@
       <c r="N117" s="17">
         <v>48.5</v>
       </c>
-      <c r="O117" s="59">
+      <c r="O117" s="58">
         <v>12.8</v>
       </c>
       <c r="P117" s="43">
@@ -8203,7 +8197,7 @@
       <c r="U117" s="45">
         <v>0</v>
       </c>
-      <c r="V117" s="131">
+      <c r="V117" s="130">
         <v>5435.0197647666273</v>
       </c>
     </row>
@@ -8234,7 +8228,7 @@
       <c r="I118" s="21">
         <v>14781</v>
       </c>
-      <c r="J118" s="62">
+      <c r="J118" s="61">
         <v>10</v>
       </c>
       <c r="K118" s="9">
@@ -8247,7 +8241,7 @@
       <c r="N118" s="17">
         <v>47.6</v>
       </c>
-      <c r="O118" s="59">
+      <c r="O118" s="58">
         <v>12.3</v>
       </c>
       <c r="P118" s="43">
@@ -8268,7 +8262,7 @@
       <c r="U118" s="45">
         <v>0</v>
       </c>
-      <c r="V118" s="131">
+      <c r="V118" s="130">
         <v>4933.6236055101244</v>
       </c>
     </row>
@@ -8299,7 +8293,7 @@
       <c r="I119" s="21">
         <v>25100</v>
       </c>
-      <c r="J119" s="62">
+      <c r="J119" s="61">
         <v>12</v>
       </c>
       <c r="K119" s="9">
@@ -8312,7 +8306,7 @@
       <c r="N119" s="17">
         <v>42.1</v>
       </c>
-      <c r="O119" s="59">
+      <c r="O119" s="58">
         <v>8.4</v>
       </c>
       <c r="P119" s="43">
@@ -8333,7 +8327,7 @@
       <c r="U119" s="45">
         <v>0</v>
       </c>
-      <c r="V119" s="131">
+      <c r="V119" s="130">
         <v>4539.8446952276945</v>
       </c>
     </row>
@@ -8364,7 +8358,7 @@
       <c r="I120" s="21">
         <v>13266</v>
       </c>
-      <c r="J120" s="62">
+      <c r="J120" s="61">
         <v>10</v>
       </c>
       <c r="K120" s="9">
@@ -8377,7 +8371,7 @@
       <c r="N120" s="17">
         <v>39.5</v>
       </c>
-      <c r="O120" s="59">
+      <c r="O120" s="58">
         <v>6.6000000000000005</v>
       </c>
       <c r="P120" s="43">
@@ -8398,7 +8392,7 @@
       <c r="U120" s="45">
         <v>0</v>
       </c>
-      <c r="V120" s="131">
+      <c r="V120" s="130">
         <v>6657.8752996374105</v>
       </c>
     </row>
@@ -8429,7 +8423,7 @@
       <c r="I121" s="21">
         <v>19130</v>
       </c>
-      <c r="J121" s="62">
+      <c r="J121" s="61">
         <v>10</v>
       </c>
       <c r="K121" s="9">
@@ -8442,7 +8436,7 @@
       <c r="N121" s="17">
         <v>46.1</v>
       </c>
-      <c r="O121" s="59">
+      <c r="O121" s="58">
         <v>6.3</v>
       </c>
       <c r="P121" s="43">
@@ -8463,7 +8457,7 @@
       <c r="U121" s="45">
         <v>0</v>
       </c>
-      <c r="V121" s="131">
+      <c r="V121" s="130">
         <v>6359.6569189797956</v>
       </c>
     </row>
@@ -8494,7 +8488,7 @@
       <c r="I122" s="21">
         <v>23663</v>
       </c>
-      <c r="J122" s="62">
+      <c r="J122" s="61">
         <v>12</v>
       </c>
       <c r="K122" s="9">
@@ -8507,7 +8501,7 @@
       <c r="N122" s="17">
         <v>49.3</v>
       </c>
-      <c r="O122" s="59">
+      <c r="O122" s="58">
         <v>1.4500000000000002</v>
       </c>
       <c r="P122" s="43">
@@ -8528,7 +8522,7 @@
       <c r="U122" s="45">
         <v>0</v>
       </c>
-      <c r="V122" s="131">
+      <c r="V122" s="130">
         <v>7924.9465988888005</v>
       </c>
     </row>
@@ -8559,7 +8553,7 @@
       <c r="I123" s="21">
         <v>39074</v>
       </c>
-      <c r="J123" s="62">
+      <c r="J123" s="61">
         <v>13</v>
       </c>
       <c r="K123" s="9">
@@ -8572,7 +8566,7 @@
       <c r="N123" s="17">
         <v>47.8</v>
       </c>
-      <c r="O123" s="59">
+      <c r="O123" s="58">
         <v>0.98</v>
       </c>
       <c r="P123" s="43">
@@ -8593,7 +8587,7 @@
       <c r="U123" s="45">
         <v>0</v>
       </c>
-      <c r="V123" s="131">
+      <c r="V123" s="130">
         <v>8588.6463113174923</v>
       </c>
     </row>
@@ -8626,7 +8620,7 @@
       <c r="I124" s="21">
         <v>74792</v>
       </c>
-      <c r="J124" s="62">
+      <c r="J124" s="61">
         <v>8</v>
       </c>
       <c r="K124" s="9">
@@ -8641,7 +8635,7 @@
       <c r="N124" s="17">
         <v>50.5</v>
       </c>
-      <c r="O124" s="59">
+      <c r="O124" s="58">
         <v>5</v>
       </c>
       <c r="P124" s="43">
@@ -8662,7 +8656,7 @@
       <c r="U124" s="45">
         <v>5.8353993499999994</v>
       </c>
-      <c r="V124" s="131">
+      <c r="V124" s="130">
         <v>7739.4202189653624</v>
       </c>
     </row>
@@ -8695,7 +8689,7 @@
       <c r="I125" s="21">
         <v>13343</v>
       </c>
-      <c r="J125" s="62">
+      <c r="J125" s="61">
         <v>8</v>
       </c>
       <c r="K125" s="9">
@@ -8710,7 +8704,7 @@
       <c r="N125" s="17">
         <v>60</v>
       </c>
-      <c r="O125" s="59">
+      <c r="O125" s="58">
         <v>7.7</v>
       </c>
       <c r="P125" s="43">
@@ -8731,7 +8725,7 @@
       <c r="U125" s="45">
         <v>33.490084196769999</v>
       </c>
-      <c r="V125" s="131">
+      <c r="V125" s="130">
         <v>5387.77000882225</v>
       </c>
     </row>
@@ -8764,7 +8758,7 @@
       <c r="I126" s="21">
         <v>14154</v>
       </c>
-      <c r="J126" s="62">
+      <c r="J126" s="61">
         <v>9</v>
       </c>
       <c r="K126" s="9">
@@ -8779,7 +8773,7 @@
       <c r="N126" s="17">
         <v>66.599999999999994</v>
       </c>
-      <c r="O126" s="59">
+      <c r="O126" s="58">
         <v>14.95</v>
       </c>
       <c r="P126" s="43">
@@ -8800,7 +8794,7 @@
       <c r="U126" s="45">
         <v>70.859890844599988</v>
       </c>
-      <c r="V126" s="131">
+      <c r="V126" s="130">
         <v>5974.5281351582798</v>
       </c>
     </row>
@@ -8833,7 +8827,7 @@
       <c r="I127" s="21">
         <v>22312</v>
       </c>
-      <c r="J127" s="62">
+      <c r="J127" s="61">
         <v>12</v>
       </c>
       <c r="K127" s="9">
@@ -8848,7 +8842,7 @@
       <c r="N127" s="17">
         <v>60.3</v>
       </c>
-      <c r="O127" s="59">
+      <c r="O127" s="58">
         <v>14.27</v>
       </c>
       <c r="P127" s="43">
@@ -8869,7 +8863,7 @@
       <c r="U127" s="45">
         <v>233.63433488066298</v>
       </c>
-      <c r="V127" s="131">
+      <c r="V127" s="130">
         <v>8160.9146189036983</v>
       </c>
     </row>
@@ -8902,7 +8896,7 @@
       <c r="I128" s="21">
         <v>32701</v>
       </c>
-      <c r="J128" s="62">
+      <c r="J128" s="61">
         <v>7</v>
       </c>
       <c r="K128" s="9">
@@ -8917,7 +8911,7 @@
       <c r="N128" s="17">
         <v>51.6</v>
       </c>
-      <c r="O128" s="59">
+      <c r="O128" s="58">
         <v>12.22</v>
       </c>
       <c r="P128" s="43">
@@ -8938,7 +8932,7 @@
       <c r="U128" s="45">
         <v>186.01556071313294</v>
       </c>
-      <c r="V128" s="131">
+      <c r="V128" s="130">
         <v>7381.4518979296026</v>
       </c>
     </row>
@@ -8971,7 +8965,7 @@
       <c r="I129" s="21">
         <v>33578</v>
       </c>
-      <c r="J129" s="62">
+      <c r="J129" s="61">
         <v>11</v>
       </c>
       <c r="K129" s="9">
@@ -8986,7 +8980,7 @@
       <c r="N129" s="17">
         <v>44.9</v>
       </c>
-      <c r="O129" s="59">
+      <c r="O129" s="58">
         <v>12.18</v>
       </c>
       <c r="P129" s="43">
@@ -9007,7 +9001,7 @@
       <c r="U129" s="45">
         <v>328.64098551165199</v>
       </c>
-      <c r="V129" s="131">
+      <c r="V129" s="130">
         <v>10179.292545540669</v>
       </c>
     </row>
@@ -9040,7 +9034,7 @@
       <c r="I130" s="21">
         <v>55554</v>
       </c>
-      <c r="J130" s="62">
+      <c r="J130" s="61">
         <v>5</v>
       </c>
       <c r="K130" s="9">
@@ -9055,7 +9049,7 @@
       <c r="N130" s="17">
         <v>38.4</v>
       </c>
-      <c r="O130" s="59">
+      <c r="O130" s="58">
         <v>14.821245286435742</v>
       </c>
       <c r="P130" s="43">
@@ -9076,7 +9070,7 @@
       <c r="U130" s="45">
         <v>390.49584979857781</v>
       </c>
-      <c r="V130" s="131">
+      <c r="V130" s="130">
         <v>10668.115163755254</v>
       </c>
     </row>
@@ -9109,7 +9103,7 @@
       <c r="I131" s="21">
         <v>41667</v>
       </c>
-      <c r="J131" s="62">
+      <c r="J131" s="61">
         <v>7</v>
       </c>
       <c r="K131" s="9">
@@ -9124,7 +9118,7 @@
       <c r="N131" s="17">
         <v>36.6</v>
       </c>
-      <c r="O131" s="64">
+      <c r="O131" s="63">
         <v>12.65166769231886</v>
       </c>
       <c r="P131" s="43">
@@ -9145,7 +9139,7 @@
       <c r="U131" s="45">
         <v>194.83693238282297</v>
       </c>
-      <c r="V131" s="131">
+      <c r="V131" s="130">
         <v>8570.4417080128369</v>
       </c>
     </row>
@@ -9178,7 +9172,7 @@
       <c r="I132" s="21">
         <v>23366</v>
       </c>
-      <c r="J132" s="62">
+      <c r="J132" s="61">
         <v>7</v>
       </c>
       <c r="K132" s="9">
@@ -9193,7 +9187,7 @@
       <c r="N132" s="17">
         <v>35.6</v>
       </c>
-      <c r="O132" s="59">
+      <c r="O132" s="58">
         <v>10.482090098201976</v>
       </c>
       <c r="P132" s="43">
@@ -9214,7 +9208,7 @@
       <c r="U132" s="45">
         <v>122.8453986730301</v>
       </c>
-      <c r="V132" s="131">
+      <c r="V132" s="130">
         <v>8262.3180803375253</v>
       </c>
     </row>
@@ -9247,7 +9241,7 @@
       <c r="I133" s="21">
         <v>19748</v>
       </c>
-      <c r="J133" s="62">
+      <c r="J133" s="61">
         <v>5</v>
       </c>
       <c r="K133" s="9">
@@ -9262,7 +9256,7 @@
       <c r="N133" s="17">
         <v>21.4</v>
       </c>
-      <c r="O133" s="59">
+      <c r="O133" s="58">
         <v>13.846153846153847</v>
       </c>
       <c r="P133" s="43">
@@ -9283,7 +9277,7 @@
       <c r="U133" s="45">
         <v>107.31960068168006</v>
       </c>
-      <c r="V133" s="131">
+      <c r="V133" s="130">
         <v>12007.582092201646</v>
       </c>
     </row>
@@ -9316,7 +9310,7 @@
       <c r="I134" s="21">
         <v>76913</v>
       </c>
-      <c r="J134" s="62">
+      <c r="J134" s="61">
         <v>3</v>
       </c>
       <c r="K134" s="9">
@@ -9331,7 +9325,7 @@
       <c r="N134" s="17">
         <v>22.6</v>
       </c>
-      <c r="O134" s="59">
+      <c r="O134" s="58">
         <v>10.5</v>
       </c>
       <c r="P134" s="43">
@@ -9352,7 +9346,7 @@
       <c r="U134" s="45">
         <v>95.262653163900026</v>
       </c>
-      <c r="V134" s="131">
+      <c r="V134" s="130">
         <v>12506.566084188891</v>
       </c>
     </row>
@@ -9385,7 +9379,7 @@
       <c r="I135" s="21">
         <v>54452</v>
       </c>
-      <c r="J135" s="62">
+      <c r="J135" s="61">
         <v>11</v>
       </c>
       <c r="K135" s="9">
@@ -9400,7 +9394,7 @@
       <c r="N135" s="17">
         <v>26.5</v>
       </c>
-      <c r="O135" s="59">
+      <c r="O135" s="58">
         <v>0.34345328567474476</v>
       </c>
       <c r="P135" s="43">
@@ -9421,7 +9415,7 @@
       <c r="U135" s="45">
         <v>62.230193495000023</v>
       </c>
-      <c r="V135" s="131">
+      <c r="V135" s="130">
         <v>17882.351960176216</v>
       </c>
     </row>
@@ -9454,7 +9448,7 @@
       <c r="I136" s="21">
         <v>95622</v>
       </c>
-      <c r="J136" s="62">
+      <c r="J136" s="61">
         <v>10</v>
       </c>
       <c r="K136" s="9">
@@ -9469,7 +9463,7 @@
       <c r="N136" s="17">
         <v>28.6</v>
       </c>
-      <c r="O136" s="59">
+      <c r="O136" s="58">
         <v>0.01</v>
       </c>
       <c r="P136" s="43">
@@ -9490,7 +9484,7 @@
       <c r="U136" s="45">
         <v>249.80307803225</v>
       </c>
-      <c r="V136" s="131">
+      <c r="V136" s="130">
         <v>13233.621131682221</v>
       </c>
     </row>
@@ -9523,7 +9517,7 @@
       <c r="I137" s="21">
         <v>66695</v>
       </c>
-      <c r="J137" s="62">
+      <c r="J137" s="61">
         <v>10</v>
       </c>
       <c r="K137" s="9">
@@ -9538,7 +9532,7 @@
       <c r="N137" s="17">
         <v>29.4</v>
       </c>
-      <c r="O137" s="59">
+      <c r="O137" s="58">
         <v>0.40950413223140492</v>
       </c>
       <c r="P137" s="43">
@@ -9559,7 +9553,7 @@
       <c r="U137" s="45">
         <v>168.90548209514981</v>
       </c>
-      <c r="V137" s="131">
+      <c r="V137" s="130">
         <v>10266.562244975174</v>
       </c>
     </row>
@@ -9592,7 +9586,7 @@
       <c r="I138" s="21">
         <v>46494</v>
       </c>
-      <c r="J138" s="62">
+      <c r="J138" s="61">
         <v>8</v>
       </c>
       <c r="K138" s="9">
@@ -9607,7 +9601,7 @@
       <c r="N138" s="17">
         <v>29.4</v>
       </c>
-      <c r="O138" s="59">
+      <c r="O138" s="58">
         <v>7.4016243893826161E-2</v>
       </c>
       <c r="P138" s="43">
@@ -9628,7 +9622,7 @@
       <c r="U138" s="45">
         <v>222.74781834074997</v>
       </c>
-      <c r="V138" s="131">
+      <c r="V138" s="130">
         <v>11092.564611427506</v>
       </c>
     </row>
@@ -9661,7 +9655,7 @@
       <c r="I139" s="21">
         <v>37629</v>
       </c>
-      <c r="J139" s="62">
+      <c r="J139" s="61">
         <v>11</v>
       </c>
       <c r="K139" s="9">
@@ -9676,7 +9670,7 @@
       <c r="N139" s="17">
         <v>35.299999999999997</v>
       </c>
-      <c r="O139" s="59">
+      <c r="O139" s="58">
         <v>0.16969182279810896</v>
       </c>
       <c r="P139" s="43">
@@ -9697,7 +9691,7 @@
       <c r="U139" s="45">
         <v>236.68125713710012</v>
       </c>
-      <c r="V139" s="131">
+      <c r="V139" s="130">
         <v>9752.5257021370999</v>
       </c>
     </row>
@@ -9730,7 +9724,7 @@
       <c r="I140" s="21">
         <v>47414</v>
       </c>
-      <c r="J140" s="62">
+      <c r="J140" s="61">
         <v>11</v>
       </c>
       <c r="K140" s="9">
@@ -9745,7 +9739,7 @@
       <c r="N140" s="17">
         <v>40.799999999999997</v>
       </c>
-      <c r="O140" s="59">
+      <c r="O140" s="58">
         <v>0.23326926209560539</v>
       </c>
       <c r="P140" s="43">
@@ -9766,7 +9760,7 @@
       <c r="U140" s="45">
         <v>133.58351726319995</v>
       </c>
-      <c r="V140" s="131">
+      <c r="V140" s="130">
         <v>9141.2399831131988</v>
       </c>
     </row>
@@ -9799,7 +9793,7 @@
       <c r="I141" s="21">
         <v>53786</v>
       </c>
-      <c r="J141" s="62">
+      <c r="J141" s="61">
         <v>10</v>
       </c>
       <c r="K141" s="9">
@@ -9814,7 +9808,7 @@
       <c r="N141" s="17">
         <v>36.799999999999997</v>
       </c>
-      <c r="O141" s="59">
+      <c r="O141" s="58">
         <v>0.32270053042176539</v>
       </c>
       <c r="P141" s="43">
@@ -9835,7 +9829,7 @@
       <c r="U141" s="45">
         <v>145.10169414039993</v>
       </c>
-      <c r="V141" s="131">
+      <c r="V141" s="130">
         <v>11699.506842811217</v>
       </c>
     </row>
@@ -9867,7 +9861,7 @@
       <c r="I142" s="21">
         <v>32383</v>
       </c>
-      <c r="J142" s="62">
+      <c r="J142" s="61">
         <v>11</v>
       </c>
       <c r="K142" s="9">
@@ -9882,7 +9876,7 @@
       <c r="N142" s="17">
         <v>33.799999999999997</v>
       </c>
-      <c r="O142" s="59">
+      <c r="O142" s="58">
         <v>9.4560482325535739E-2</v>
       </c>
       <c r="P142" s="43">
@@ -9903,7 +9897,7 @@
       <c r="U142" s="45">
         <v>228.2370238142</v>
       </c>
-      <c r="V142" s="131">
+      <c r="V142" s="130">
         <v>13147.100863664196</v>
       </c>
     </row>
@@ -9935,7 +9929,7 @@
       <c r="I143" s="21">
         <v>242704</v>
       </c>
-      <c r="J143" s="62">
+      <c r="J143" s="61">
         <v>11</v>
       </c>
       <c r="K143" s="9">
@@ -9950,7 +9944,7 @@
       <c r="N143" s="17">
         <v>29.1</v>
       </c>
-      <c r="O143" s="59">
+      <c r="O143" s="58">
         <v>3.3322116563821766E-2</v>
       </c>
       <c r="P143" s="43">
@@ -9971,7 +9965,7 @@
       <c r="U143" s="45">
         <v>182.06499892710002</v>
       </c>
-      <c r="V143" s="131">
+      <c r="V143" s="130">
         <v>15716.959059317122</v>
       </c>
     </row>
@@ -10003,7 +9997,7 @@
       <c r="I144" s="21">
         <v>63715</v>
       </c>
-      <c r="J144" s="62">
+      <c r="J144" s="61">
         <v>12</v>
       </c>
       <c r="K144" s="9">
@@ -10018,7 +10012,7 @@
       <c r="N144" s="17">
         <v>33.299999999999997</v>
       </c>
-      <c r="O144" s="59">
+      <c r="O144" s="58">
         <v>0.63985417871685957</v>
       </c>
       <c r="P144" s="43">
@@ -10039,7 +10033,7 @@
       <c r="U144" s="45">
         <v>218.63431473280005</v>
       </c>
-      <c r="V144" s="131">
+      <c r="V144" s="130">
         <v>17806.266828033993</v>
       </c>
     </row>
@@ -10071,7 +10065,7 @@
       <c r="I145" s="21">
         <v>78368</v>
       </c>
-      <c r="J145" s="62">
+      <c r="J145" s="61">
         <v>10</v>
       </c>
       <c r="K145" s="9">
@@ -10086,7 +10080,7 @@
       <c r="N145" s="17">
         <v>34.299999999999997</v>
       </c>
-      <c r="O145" s="59">
+      <c r="O145" s="58">
         <v>1.4856925837657313</v>
       </c>
       <c r="P145" s="43">
@@ -10107,7 +10101,7 @@
       <c r="U145" s="45">
         <v>266.44832406130001</v>
       </c>
-      <c r="V145" s="131">
+      <c r="V145" s="130">
         <v>21985.495056871681</v>
       </c>
     </row>
@@ -10139,7 +10133,7 @@
       <c r="I146" s="21">
         <v>54124</v>
       </c>
-      <c r="J146" s="62">
+      <c r="J146" s="61">
         <v>9</v>
       </c>
       <c r="K146" s="9">
@@ -10154,7 +10148,7 @@
       <c r="N146" s="17">
         <v>33.5</v>
       </c>
-      <c r="O146" s="59">
+      <c r="O146" s="58">
         <v>1.6532147572404425</v>
       </c>
       <c r="P146" s="43">
@@ -10175,7 +10169,7 @@
       <c r="U146" s="45">
         <v>277.45377918049991</v>
       </c>
-      <c r="V146" s="131">
+      <c r="V146" s="130">
         <v>26376.938378880535</v>
       </c>
     </row>
@@ -10207,7 +10201,7 @@
       <c r="I147" s="21">
         <v>86979</v>
       </c>
-      <c r="J147" s="62">
+      <c r="J147" s="61">
         <v>16</v>
       </c>
       <c r="K147" s="9">
@@ -10222,7 +10216,7 @@
       <c r="N147" s="17">
         <v>36</v>
       </c>
-      <c r="O147" s="59">
+      <c r="O147" s="58">
         <v>2.987096685032653</v>
       </c>
       <c r="P147" s="43">
@@ -10243,7 +10237,7 @@
       <c r="U147" s="45">
         <v>312.73087898119991</v>
       </c>
-      <c r="V147" s="131">
+      <c r="V147" s="130">
         <v>29674.644667058619</v>
       </c>
     </row>
@@ -10275,7 +10269,7 @@
       <c r="I148" s="21">
         <v>116413</v>
       </c>
-      <c r="J148" s="62">
+      <c r="J148" s="61">
         <v>9</v>
       </c>
       <c r="K148" s="9">
@@ -10290,7 +10284,7 @@
       <c r="N148" s="17">
         <v>38.6</v>
       </c>
-      <c r="O148" s="59">
+      <c r="O148" s="58">
         <v>4.270461401994095</v>
       </c>
       <c r="P148" s="43">
@@ -10311,7 +10305,7 @@
       <c r="U148" s="45">
         <v>300.60411708340001</v>
       </c>
-      <c r="V148" s="131">
+      <c r="V148" s="130">
         <v>22291.08500460595</v>
       </c>
     </row>
@@ -10343,7 +10337,7 @@
       <c r="I149" s="21">
         <v>95347</v>
       </c>
-      <c r="J149" s="62">
+      <c r="J149" s="61">
         <v>17</v>
       </c>
       <c r="K149" s="9">
@@ -10358,7 +10352,7 @@
       <c r="N149" s="17">
         <v>39.4</v>
       </c>
-      <c r="O149" s="59">
+      <c r="O149" s="58">
         <v>4.82014730464401</v>
       </c>
       <c r="P149" s="43">
@@ -10379,7 +10373,7 @@
       <c r="U149" s="45">
         <v>290.96568330320002</v>
       </c>
-      <c r="V149" s="131">
+      <c r="V149" s="130">
         <v>21193.868874413201</v>
       </c>
     </row>
@@ -10411,7 +10405,7 @@
       <c r="I150" s="21">
         <v>70543</v>
       </c>
-      <c r="J150" s="62">
+      <c r="J150" s="61">
         <v>14</v>
       </c>
       <c r="K150" s="9">
@@ -10426,7 +10420,7 @@
       <c r="N150" s="17">
         <v>40.799999999999997</v>
       </c>
-      <c r="O150" s="59">
+      <c r="O150" s="58">
         <v>4.6651094945505633</v>
       </c>
       <c r="P150" s="43">
@@ -10447,7 +10441,7 @@
       <c r="U150" s="45">
         <v>350.7333772467</v>
       </c>
-      <c r="V150" s="131">
+      <c r="V150" s="130">
         <v>23348.387228397143</v>
       </c>
     </row>
@@ -10479,7 +10473,7 @@
       <c r="I151" s="21">
         <v>48488</v>
       </c>
-      <c r="J151" s="62">
+      <c r="J151" s="61">
         <v>8</v>
       </c>
       <c r="K151" s="9">
@@ -10494,7 +10488,7 @@
       <c r="N151" s="17">
         <v>41.7</v>
       </c>
-      <c r="O151" s="59">
+      <c r="O151" s="58">
         <v>4.089989521127527</v>
       </c>
       <c r="P151" s="43">
@@ -10515,7 +10509,7 @@
       <c r="U151" s="45">
         <v>619.74846248580013</v>
       </c>
-      <c r="V151" s="131">
+      <c r="V151" s="130">
         <v>25841.49081074027</v>
       </c>
     </row>
@@ -10547,7 +10541,7 @@
       <c r="I152" s="21">
         <v>66984</v>
       </c>
-      <c r="J152" s="62">
+      <c r="J152" s="61">
         <v>17</v>
       </c>
       <c r="K152" s="9">
@@ -10562,7 +10556,7 @@
       <c r="N152" s="17">
         <v>42.4</v>
       </c>
-      <c r="O152" s="59">
+      <c r="O152" s="58">
         <v>0.35202293127496126</v>
       </c>
       <c r="P152" s="43">
@@ -10583,7 +10577,7 @@
       <c r="U152" s="45">
         <v>645.04472750240006</v>
       </c>
-      <c r="V152" s="131">
+      <c r="V152" s="130">
         <v>27962.368320239504</v>
       </c>
     </row>
@@ -10615,7 +10609,7 @@
       <c r="I153" s="21">
         <v>86335</v>
       </c>
-      <c r="J153" s="62">
+      <c r="J153" s="61">
         <v>12</v>
       </c>
       <c r="K153" s="9">
@@ -10630,7 +10624,7 @@
       <c r="N153" s="17">
         <v>42.9</v>
       </c>
-      <c r="O153" s="59">
+      <c r="O153" s="58">
         <v>1.226070627702724</v>
       </c>
       <c r="P153" s="43">
@@ -10651,7 +10645,7 @@
       <c r="U153" s="45">
         <v>546.89201805610014</v>
       </c>
-      <c r="V153" s="131">
+      <c r="V153" s="130">
         <v>23091.809628362938</v>
       </c>
     </row>
@@ -10683,7 +10677,7 @@
       <c r="I154" s="21">
         <v>49626</v>
       </c>
-      <c r="J154" s="62">
+      <c r="J154" s="61">
         <v>5</v>
       </c>
       <c r="K154" s="9">
@@ -10698,7 +10692,7 @@
       <c r="N154" s="17">
         <v>41.1</v>
       </c>
-      <c r="O154" s="59">
+      <c r="O154" s="58">
         <v>1.1803196197570995</v>
       </c>
       <c r="P154" s="43">
@@ -10719,7 +10713,7 @@
       <c r="U154" s="45">
         <v>774.98080437339991</v>
       </c>
-      <c r="V154" s="131">
+      <c r="V154" s="130">
         <v>22652.739036887404</v>
       </c>
     </row>
@@ -10751,7 +10745,7 @@
       <c r="I155" s="21">
         <v>93902</v>
       </c>
-      <c r="J155" s="62">
+      <c r="J155" s="61">
         <v>9</v>
       </c>
       <c r="K155" s="9">
@@ -10766,7 +10760,7 @@
       <c r="N155" s="17">
         <v>41</v>
       </c>
-      <c r="O155" s="59">
+      <c r="O155" s="58">
         <v>1.3074754072794994</v>
       </c>
       <c r="P155" s="43">
@@ -10787,7 +10781,7 @@
       <c r="U155" s="45">
         <v>509.15362720799988</v>
       </c>
-      <c r="V155" s="131">
+      <c r="V155" s="130">
         <v>21541.693884428299</v>
       </c>
     </row>
@@ -10819,7 +10813,7 @@
       <c r="I156" s="21">
         <v>64676</v>
       </c>
-      <c r="J156" s="62">
+      <c r="J156" s="61">
         <v>17</v>
       </c>
       <c r="K156" s="9">
@@ -10834,7 +10828,7 @@
       <c r="N156" s="17">
         <v>43.3</v>
       </c>
-      <c r="O156" s="59">
+      <c r="O156" s="58">
         <v>2.8382608822765936</v>
       </c>
       <c r="P156" s="43">
@@ -10855,7 +10849,7 @@
       <c r="U156" s="45">
         <v>374.93932076976796</v>
       </c>
-      <c r="V156" s="131">
+      <c r="V156" s="130">
         <v>34036.765195074746</v>
       </c>
     </row>
@@ -10887,7 +10881,7 @@
       <c r="I157" s="21">
         <v>67636</v>
       </c>
-      <c r="J157" s="62">
+      <c r="J157" s="61">
         <v>13</v>
       </c>
       <c r="K157" s="9">
@@ -10902,7 +10896,7 @@
       <c r="N157" s="17">
         <v>45.7</v>
       </c>
-      <c r="O157" s="59">
+      <c r="O157" s="58">
         <v>9.9736507750615218</v>
       </c>
       <c r="P157" s="43">
@@ -10923,7 +10917,7 @@
       <c r="U157" s="45">
         <v>333.84866539609993</v>
       </c>
-      <c r="V157" s="131">
+      <c r="V157" s="130">
         <v>34820.478071705678</v>
       </c>
     </row>
@@ -10955,7 +10949,7 @@
       <c r="I158" s="21">
         <v>107972</v>
       </c>
-      <c r="J158" s="62">
+      <c r="J158" s="61">
         <v>16</v>
       </c>
       <c r="K158" s="9">
@@ -10970,7 +10964,7 @@
       <c r="N158" s="17">
         <v>47.3</v>
       </c>
-      <c r="O158" s="59">
+      <c r="O158" s="58">
         <v>0.3499677902644866</v>
       </c>
       <c r="P158" s="43">
@@ -10991,7 +10985,7 @@
       <c r="U158" s="45">
         <v>490.18662846099983</v>
       </c>
-      <c r="V158" s="131">
+      <c r="V158" s="130">
         <v>43371.139915373948</v>
       </c>
     </row>
@@ -11023,7 +11017,7 @@
       <c r="I159" s="21">
         <v>124137</v>
       </c>
-      <c r="J159" s="62">
+      <c r="J159" s="61">
         <v>15</v>
       </c>
       <c r="K159" s="9">
@@ -11038,7 +11032,7 @@
       <c r="N159" s="17">
         <v>50.5</v>
       </c>
-      <c r="O159" s="59">
+      <c r="O159" s="58">
         <v>0.11019716073389979</v>
       </c>
       <c r="P159" s="43">
@@ -11059,7 +11053,7 @@
       <c r="U159" s="45">
         <v>704.76279948210004</v>
       </c>
-      <c r="V159" s="131">
+      <c r="V159" s="130">
         <v>42437.228393575002</v>
       </c>
     </row>
@@ -11091,7 +11085,7 @@
       <c r="I160" s="21">
         <v>183408</v>
       </c>
-      <c r="J160" s="62">
+      <c r="J160" s="61">
         <v>10</v>
       </c>
       <c r="K160" s="9">
@@ -11106,7 +11100,7 @@
       <c r="N160" s="17">
         <v>53.5</v>
       </c>
-      <c r="O160" s="59">
+      <c r="O160" s="58">
         <v>-0.35165393921139226</v>
       </c>
       <c r="P160" s="43">
@@ -11127,7 +11121,7 @@
       <c r="U160" s="45">
         <v>1110.2804907018999</v>
       </c>
-      <c r="V160" s="131">
+      <c r="V160" s="130">
         <v>66963.031260458491</v>
       </c>
     </row>
@@ -11159,7 +11153,7 @@
       <c r="I161" s="21">
         <v>172639</v>
       </c>
-      <c r="J161" s="62">
+      <c r="J161" s="61">
         <v>12</v>
       </c>
       <c r="K161" s="9">
@@ -11174,7 +11168,7 @@
       <c r="N161" s="17">
         <v>62.8</v>
       </c>
-      <c r="O161" s="59">
+      <c r="O161" s="58">
         <v>-0.10159638951234684</v>
       </c>
       <c r="P161" s="43">
@@ -11195,7 +11189,7 @@
       <c r="U161" s="45">
         <v>449.7980591455601</v>
       </c>
-      <c r="V161" s="131">
+      <c r="V161" s="130">
         <v>57318.466429089429</v>
       </c>
     </row>
@@ -11227,7 +11221,7 @@
       <c r="I162" s="21">
         <v>146536</v>
       </c>
-      <c r="J162" s="62">
+      <c r="J162" s="61">
         <v>10</v>
       </c>
       <c r="K162" s="9">
@@ -11242,7 +11236,7 @@
       <c r="N162" s="17">
         <v>70.5</v>
       </c>
-      <c r="O162" s="59">
+      <c r="O162" s="58">
         <v>5.3106749408772504E-2</v>
       </c>
       <c r="P162" s="43">
@@ -11263,7 +11257,7 @@
       <c r="U162" s="45">
         <v>500.32474159800023</v>
       </c>
-      <c r="V162" s="131">
+      <c r="V162" s="130">
         <v>63215.008329018623</v>
       </c>
     </row>
@@ -11295,7 +11289,7 @@
       <c r="I163" s="21">
         <v>101131</v>
       </c>
-      <c r="J163" s="62">
+      <c r="J163" s="61">
         <v>10</v>
       </c>
       <c r="K163" s="9">
@@ -11310,7 +11304,7 @@
       <c r="N163" s="17">
         <v>74.900000000000006</v>
       </c>
-      <c r="O163" s="59">
+      <c r="O163" s="58">
         <v>0.3107786777228595</v>
       </c>
       <c r="P163" s="43">
@@ -11331,7 +11325,7 @@
       <c r="U163" s="45">
         <v>2090.2578169509993</v>
       </c>
-      <c r="V163" s="131">
+      <c r="V163" s="130">
         <v>59803.765376824369</v>
       </c>
     </row>
@@ -11363,7 +11357,7 @@
       <c r="I164" s="21">
         <v>229336</v>
       </c>
-      <c r="J164" s="62">
+      <c r="J164" s="61">
         <v>16</v>
       </c>
       <c r="K164" s="9">
@@ -11378,7 +11372,7 @@
       <c r="N164" s="17">
         <v>77.3</v>
       </c>
-      <c r="O164" s="59">
+      <c r="O164" s="58">
         <v>0.61932095275490473</v>
       </c>
       <c r="P164" s="43">
@@ -11399,7 +11393,7 @@
       <c r="U164" s="45">
         <v>1528.1143262683001</v>
       </c>
-      <c r="V164" s="131">
+      <c r="V164" s="130">
         <v>75712.195441758086</v>
       </c>
     </row>
@@ -11431,7 +11425,7 @@
       <c r="I165" s="21">
         <v>190521</v>
       </c>
-      <c r="J165" s="62">
+      <c r="J165" s="61">
         <v>21</v>
       </c>
       <c r="K165" s="9">
@@ -11446,7 +11440,7 @@
       <c r="N165" s="17">
         <v>78</v>
       </c>
-      <c r="O165" s="59">
+      <c r="O165" s="58">
         <v>0.24420528792282434</v>
       </c>
       <c r="P165" s="43">
@@ -11467,7 +11461,7 @@
       <c r="U165" s="45">
         <v>1147.1719216837</v>
       </c>
-      <c r="V165" s="131">
+      <c r="V165" s="130">
         <v>83460.654554519409</v>
       </c>
     </row>
@@ -11499,7 +11493,7 @@
       <c r="I166" s="21">
         <v>261644</v>
       </c>
-      <c r="J166" s="62">
+      <c r="J166" s="61">
         <v>8</v>
       </c>
       <c r="K166" s="9">
@@ -11514,7 +11508,7 @@
       <c r="N166" s="17">
         <v>77.8</v>
       </c>
-      <c r="O166" s="59">
+      <c r="O166" s="58">
         <v>0.34905403787030437</v>
       </c>
       <c r="P166" s="43">
@@ -11535,7 +11529,7 @@
       <c r="U166" s="45">
         <v>1408.8094451250997</v>
       </c>
-      <c r="V166" s="131">
+      <c r="V166" s="130">
         <v>96318.368337511391</v>
       </c>
     </row>
@@ -11567,7 +11561,7 @@
       <c r="I167" s="21">
         <v>252915</v>
       </c>
-      <c r="J167" s="62">
+      <c r="J167" s="61">
         <v>10</v>
       </c>
       <c r="K167" s="9">
@@ -11582,7 +11576,7 @@
       <c r="N167" s="17">
         <v>77.400000000000006</v>
       </c>
-      <c r="O167" s="59">
+      <c r="O167" s="58">
         <v>0.4156081057594791</v>
       </c>
       <c r="P167" s="43">
@@ -11603,7 +11597,7 @@
       <c r="U167" s="45">
         <v>865.22292571850005</v>
       </c>
-      <c r="V167" s="131">
+      <c r="V167" s="130">
         <v>88005.489847613309</v>
       </c>
     </row>
@@ -11635,7 +11629,7 @@
       <c r="I168" s="21">
         <v>364277</v>
       </c>
-      <c r="J168" s="62">
+      <c r="J168" s="61">
         <v>12</v>
       </c>
       <c r="K168" s="9">
@@ -11650,7 +11644,7 @@
       <c r="N168" s="17">
         <v>78</v>
       </c>
-      <c r="O168" s="59">
+      <c r="O168" s="58">
         <v>0.39655012273691825</v>
       </c>
       <c r="P168" s="43">
@@ -11671,7 +11665,7 @@
       <c r="U168" s="45">
         <v>1138.3945769039003</v>
       </c>
-      <c r="V168" s="131">
+      <c r="V168" s="130">
         <v>139577.06138249984</v>
       </c>
     </row>
@@ -11703,7 +11697,7 @@
       <c r="I169" s="21">
         <v>335049</v>
       </c>
-      <c r="J169" s="62">
+      <c r="J169" s="61">
         <v>8</v>
       </c>
       <c r="K169" s="9">
@@ -11718,7 +11712,7 @@
       <c r="N169" s="17">
         <v>80.599999999999994</v>
       </c>
-      <c r="O169" s="59">
+      <c r="O169" s="58">
         <v>8.8126398191315652E-2</v>
       </c>
       <c r="P169" s="43">
@@ -11739,7 +11733,7 @@
       <c r="U169" s="45">
         <v>1813.1895784881999</v>
       </c>
-      <c r="V169" s="131">
+      <c r="V169" s="130">
         <v>129603.39977605635</v>
       </c>
     </row>
@@ -11771,7 +11765,7 @@
       <c r="I170" s="21">
         <v>256140</v>
       </c>
-      <c r="J170" s="62">
+      <c r="J170" s="61">
         <v>8</v>
       </c>
       <c r="K170" s="9">
@@ -11786,7 +11780,7 @@
       <c r="N170" s="17">
         <v>93.7</v>
       </c>
-      <c r="O170" s="59">
+      <c r="O170" s="58">
         <v>-2.3626666400578511</v>
       </c>
       <c r="P170" s="43">
@@ -11807,7 +11801,7 @@
       <c r="U170" s="45">
         <v>1691.5740037592</v>
       </c>
-      <c r="V170" s="131">
+      <c r="V170" s="130">
         <v>113528.19857791653</v>
       </c>
     </row>
@@ -11839,7 +11833,7 @@
       <c r="I171" s="21">
         <v>434734</v>
       </c>
-      <c r="J171" s="62">
+      <c r="J171" s="61">
         <v>16</v>
       </c>
       <c r="K171" s="9">
@@ -11854,7 +11848,7 @@
       <c r="N171" s="17">
         <v>96</v>
       </c>
-      <c r="O171" s="59">
+      <c r="O171" s="58">
         <v>-7.24</v>
       </c>
       <c r="P171" s="43">
@@ -11875,7 +11869,7 @@
       <c r="U171" s="45">
         <v>2315.0673424045417</v>
       </c>
-      <c r="V171" s="131">
+      <c r="V171" s="130">
         <v>167614.73214594575</v>
       </c>
     </row>
@@ -11907,7 +11901,7 @@
       <c r="I172" s="21">
         <v>436832</v>
       </c>
-      <c r="J172" s="62">
+      <c r="J172" s="61">
         <v>17</v>
       </c>
       <c r="K172" s="9">
@@ -11922,7 +11916,7 @@
       <c r="N172" s="17">
         <v>98.2</v>
       </c>
-      <c r="O172" s="59">
+      <c r="O172" s="58">
         <v>-4.2859960056711808</v>
       </c>
       <c r="P172" s="43">
@@ -11943,7 +11937,7 @@
       <c r="U172" s="45">
         <v>1908.7984767749488</v>
       </c>
-      <c r="V172" s="131">
+      <c r="V172" s="130">
         <v>160994.02211170096</v>
       </c>
     </row>
@@ -11975,7 +11969,7 @@
       <c r="I173" s="21">
         <v>314193</v>
       </c>
-      <c r="J173" s="62">
+      <c r="J173" s="61">
         <v>7</v>
       </c>
       <c r="K173" s="9">
@@ -11990,7 +11984,7 @@
       <c r="N173" s="17">
         <v>104.4</v>
       </c>
-      <c r="O173" s="59">
+      <c r="O173" s="58">
         <v>-6.3905579397136041</v>
       </c>
       <c r="P173" s="43">
@@ -12011,7 +12005,7 @@
       <c r="U173" s="45">
         <v>2182.7905224137094</v>
       </c>
-      <c r="V173" s="131">
+      <c r="V173" s="130">
         <v>215484.18740553226</v>
       </c>
     </row>
@@ -12043,7 +12037,7 @@
       <c r="I174" s="21">
         <v>582741</v>
       </c>
-      <c r="J174" s="62">
+      <c r="J174" s="61">
         <v>14</v>
       </c>
       <c r="K174" s="9">
@@ -12058,7 +12052,7 @@
       <c r="N174" s="17">
         <v>116.5</v>
       </c>
-      <c r="O174" s="59">
+      <c r="O174" s="58">
         <v>-8.4453237503265459</v>
       </c>
       <c r="P174" s="43">
@@ -12079,7 +12073,7 @@
       <c r="U174" s="45">
         <v>4360.7982767548019</v>
       </c>
-      <c r="V174" s="131">
+      <c r="V174" s="130">
         <v>231315.06632699858</v>
       </c>
     </row>
@@ -12111,7 +12105,7 @@
       <c r="I175" s="21">
         <v>651172</v>
       </c>
-      <c r="J175" s="62">
+      <c r="J175" s="61">
         <v>7</v>
       </c>
       <c r="K175" s="9">
@@ -12126,7 +12120,7 @@
       <c r="N175" s="17">
         <v>131.4</v>
       </c>
-      <c r="O175" s="59">
+      <c r="O175" s="58">
         <v>-14.913887594818439</v>
       </c>
       <c r="P175" s="43">
@@ -12147,7 +12141,7 @@
       <c r="U175" s="45">
         <v>2634.5256216512207</v>
       </c>
-      <c r="V175" s="131">
+      <c r="V175" s="130">
         <v>286820.46590742632</v>
       </c>
     </row>
@@ -12179,7 +12173,7 @@
       <c r="I176" s="21">
         <v>433646</v>
       </c>
-      <c r="J176" s="62">
+      <c r="J176" s="61">
         <v>10</v>
       </c>
       <c r="K176" s="9">
@@ -12194,7 +12188,7 @@
       <c r="N176" s="17">
         <v>129.4</v>
       </c>
-      <c r="O176" s="59">
+      <c r="O176" s="58">
         <v>-29.953844365463674</v>
       </c>
       <c r="P176" s="43">
@@ -12215,7 +12209,7 @@
       <c r="U176" s="45">
         <v>3284.1457763956</v>
       </c>
-      <c r="V176" s="131">
+      <c r="V176" s="130">
         <v>262478.17684078281</v>
       </c>
     </row>
@@ -12247,7 +12241,7 @@
       <c r="I177" s="21">
         <v>433404</v>
       </c>
-      <c r="J177" s="62">
+      <c r="J177" s="61">
         <v>7</v>
       </c>
       <c r="K177" s="9">
@@ -12262,7 +12256,7 @@
       <c r="N177" s="17">
         <v>116.9</v>
       </c>
-      <c r="O177" s="59">
+      <c r="O177" s="58">
         <v>-15.280418048968263</v>
       </c>
       <c r="P177" s="43">
@@ -12283,7 +12277,7 @@
       <c r="U177" s="45">
         <v>5414.6350379000014</v>
       </c>
-      <c r="V177" s="131">
+      <c r="V177" s="130">
         <v>329778.4758091601</v>
       </c>
     </row>
@@ -12315,7 +12309,7 @@
       <c r="I178" s="21">
         <v>1286150</v>
       </c>
-      <c r="J178" s="62">
+      <c r="J178" s="61">
         <v>4</v>
       </c>
       <c r="K178" s="9">
@@ -12330,7 +12324,7 @@
       <c r="N178" s="17">
         <v>102.5</v>
       </c>
-      <c r="O178" s="59">
+      <c r="O178" s="58">
         <v>1.4719276725599262</v>
       </c>
       <c r="P178" s="43">
@@ -12351,7 +12345,7 @@
       <c r="U178" s="45">
         <v>5655.9519398470002</v>
       </c>
-      <c r="V178" s="131">
+      <c r="V178" s="130">
         <v>444891.87732220639</v>
       </c>
     </row>
@@ -12383,7 +12377,7 @@
       <c r="I179" s="21">
         <v>857819</v>
       </c>
-      <c r="J179" s="62">
+      <c r="J179" s="61">
         <v>9</v>
       </c>
       <c r="K179" s="9">
@@ -12398,7 +12392,7 @@
       <c r="N179" s="17">
         <v>103.1</v>
       </c>
-      <c r="O179" s="59">
+      <c r="O179" s="58">
         <v>2.0782748241925688</v>
       </c>
       <c r="P179" s="43">
@@ -12419,7 +12413,7 @@
       <c r="U179" s="45">
         <v>7841.7780289588563</v>
       </c>
-      <c r="V179" s="131">
+      <c r="V179" s="130">
         <v>421877.03609497129</v>
       </c>
     </row>
@@ -12451,7 +12445,7 @@
       <c r="I180" s="21">
         <v>990519</v>
       </c>
-      <c r="J180" s="62">
+      <c r="J180" s="61">
         <v>8</v>
       </c>
       <c r="K180" s="9">
@@ -12466,7 +12460,7 @@
       <c r="N180" s="17">
         <v>87.6</v>
       </c>
-      <c r="O180" s="59">
+      <c r="O180" s="58">
         <v>5.5776909826943406</v>
       </c>
       <c r="P180" s="43">
@@ -12487,7 +12481,7 @@
       <c r="U180" s="45">
         <v>8766.7934674155167</v>
       </c>
-      <c r="V180" s="131">
+      <c r="V180" s="130">
         <v>504512.15643104317</v>
       </c>
     </row>
@@ -12519,7 +12513,7 @@
       <c r="I181" s="21">
         <v>1538286</v>
       </c>
-      <c r="J181" s="62">
+      <c r="J181" s="61">
         <v>9</v>
       </c>
       <c r="K181" s="9">
@@ -12534,7 +12528,7 @@
       <c r="N181" s="17">
         <v>70.900000000000006</v>
       </c>
-      <c r="O181" s="59">
+      <c r="O181" s="58">
         <v>7.930512615927757</v>
       </c>
       <c r="P181" s="43">
@@ -12555,7 +12549,7 @@
       <c r="U181" s="45">
         <v>10322.239052329996</v>
       </c>
-      <c r="V181" s="131">
+      <c r="V181" s="130">
         <v>738973.61274585431</v>
       </c>
     </row>
@@ -12587,7 +12581,7 @@
       <c r="I182" s="21">
         <v>1299707</v>
       </c>
-      <c r="J182" s="62">
+      <c r="J182" s="61">
         <v>10</v>
       </c>
       <c r="K182" s="9">
@@ -12602,7 +12596,7 @@
       <c r="N182" s="17">
         <v>45</v>
       </c>
-      <c r="O182" s="59">
+      <c r="O182" s="58">
         <v>6.4339299736404758</v>
       </c>
       <c r="P182" s="43">
@@ -12623,7 +12617,7 @@
       <c r="U182" s="45">
         <v>13461.261348100541</v>
       </c>
-      <c r="V182" s="131">
+      <c r="V182" s="130">
         <v>729161.75943937025</v>
       </c>
     </row>
@@ -12655,7 +12649,7 @@
       <c r="I183" s="21">
         <v>1634140</v>
       </c>
-      <c r="J183" s="62">
+      <c r="J183" s="61">
         <v>10</v>
       </c>
       <c r="K183" s="9">
@@ -12670,7 +12664,7 @@
       <c r="N183" s="17">
         <v>42.2</v>
       </c>
-      <c r="O183" s="59">
+      <c r="O183" s="58">
         <v>2.3466882705542149</v>
       </c>
       <c r="P183" s="43">
@@ -12691,7 +12685,7 @@
       <c r="U183" s="45">
         <v>7216.5911462239828</v>
       </c>
-      <c r="V183" s="131">
+      <c r="V183" s="130">
         <v>729448.00756812969</v>
       </c>
     </row>
@@ -12723,7 +12717,7 @@
       <c r="I184" s="21">
         <v>2603653.7499850001</v>
       </c>
-      <c r="J184" s="62">
+      <c r="J184" s="61">
         <v>10</v>
       </c>
       <c r="K184" s="9">
@@ -12738,7 +12732,7 @@
       <c r="N184" s="17">
         <v>46.3</v>
       </c>
-      <c r="O184" s="59">
+      <c r="O184" s="58">
         <v>0.63675375317123273</v>
       </c>
       <c r="P184" s="43">
@@ -12759,7 +12753,7 @@
       <c r="U184" s="45">
         <v>9872.6313206309551</v>
       </c>
-      <c r="V184" s="131">
+      <c r="V184" s="130">
         <v>1085575.031158292</v>
       </c>
     </row>
@@ -12791,7 +12785,7 @@
       <c r="I185" s="21">
         <v>1743594</v>
       </c>
-      <c r="J185" s="62">
+      <c r="J185" s="61">
         <v>13</v>
       </c>
       <c r="K185" s="9">
@@ -12806,7 +12800,7 @@
       <c r="N185" s="17">
         <v>47.6</v>
       </c>
-      <c r="O185" s="59">
+      <c r="O185" s="58">
         <v>1.856258784152873</v>
       </c>
       <c r="P185" s="43">
@@ -12827,7 +12821,7 @@
       <c r="U185" s="45">
         <v>13418.205792148208</v>
       </c>
-      <c r="V185" s="131">
+      <c r="V185" s="130">
         <v>829456.87572663266</v>
       </c>
     </row>
@@ -12859,7 +12853,7 @@
       <c r="I186" s="21">
         <v>2281366.1219660002</v>
       </c>
-      <c r="J186" s="62">
+      <c r="J186" s="61">
         <v>10</v>
       </c>
       <c r="K186" s="9">
@@ -12874,7 +12868,7 @@
       <c r="N186" s="17">
         <v>49.8</v>
       </c>
-      <c r="O186" s="59">
+      <c r="O186" s="58">
         <v>4.3007550150496803</v>
       </c>
       <c r="P186" s="43">
@@ -12895,7 +12889,7 @@
       <c r="U186" s="45">
         <v>10881.760549940465</v>
       </c>
-      <c r="V186" s="131">
+      <c r="V186" s="130">
         <v>850953.44805030979</v>
       </c>
     </row>
@@ -12927,7 +12921,7 @@
       <c r="I187" s="21">
         <v>3868547</v>
       </c>
-      <c r="J187" s="62">
+      <c r="J187" s="61">
         <v>16</v>
       </c>
       <c r="K187" s="9">
@@ -12942,7 +12936,7 @@
       <c r="N187" s="17">
         <v>50.3</v>
       </c>
-      <c r="O187" s="59">
+      <c r="O187" s="58">
         <v>6.4278657378711443</v>
       </c>
       <c r="P187" s="43">
@@ -12963,7 +12957,7 @@
       <c r="U187" s="45">
         <v>16103.39322249265</v>
       </c>
-      <c r="V187" s="131">
+      <c r="V187" s="130">
         <v>966704.41150283674</v>
       </c>
     </row>
@@ -12995,7 +12989,7 @@
       <c r="I188" s="21">
         <v>2347454</v>
       </c>
-      <c r="J188" s="62">
+      <c r="J188" s="61">
         <v>9</v>
       </c>
       <c r="K188" s="9">
@@ -13010,7 +13004,7 @@
       <c r="N188" s="17">
         <v>45</v>
       </c>
-      <c r="O188" s="59">
+      <c r="O188" s="58">
         <v>7.1929799152564051</v>
       </c>
       <c r="P188" s="43">
@@ -13031,7 +13025,7 @@
       <c r="U188" s="45">
         <v>10586.899246725559</v>
       </c>
-      <c r="V188" s="131">
+      <c r="V188" s="130">
         <v>868031.1167032473</v>
       </c>
     </row>
@@ -13063,7 +13057,7 @@
       <c r="I189" s="21">
         <v>3166117</v>
       </c>
-      <c r="J189" s="62">
+      <c r="J189" s="61">
         <v>18</v>
       </c>
       <c r="K189" s="9">
@@ -13078,7 +13072,7 @@
       <c r="N189" s="17">
         <v>41</v>
       </c>
-      <c r="O189" s="59">
+      <c r="O189" s="58">
         <v>6.8835758167178644</v>
       </c>
       <c r="P189" s="43">
@@ -13099,10 +13093,10 @@
       <c r="U189" s="45">
         <v>12010.749659115261</v>
       </c>
-      <c r="V189" s="131">
+      <c r="V189" s="130">
         <v>842923.57459634007</v>
       </c>
-      <c r="W189" s="100"/>
+      <c r="W189" s="99"/>
     </row>
     <row r="190" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
@@ -13132,7 +13126,7 @@
       <c r="I190" s="21">
         <v>3380457.991157</v>
       </c>
-      <c r="J190" s="62">
+      <c r="J190" s="61">
         <v>8</v>
       </c>
       <c r="K190" s="9">
@@ -13147,7 +13141,7 @@
       <c r="N190" s="17">
         <v>39</v>
       </c>
-      <c r="O190" s="59">
+      <c r="O190" s="58">
         <v>9.5335373033505704</v>
       </c>
       <c r="P190" s="43">
@@ -13168,7 +13162,7 @@
       <c r="U190" s="45">
         <v>15721.614616017729</v>
       </c>
-      <c r="V190" s="131">
+      <c r="V190" s="130">
         <v>783986.56366171606</v>
       </c>
     </row>
@@ -13200,7 +13194,7 @@
       <c r="I191" s="21">
         <v>2594429</v>
       </c>
-      <c r="J191" s="62">
+      <c r="J191" s="61">
         <v>12</v>
       </c>
       <c r="K191" s="9">
@@ -13215,7 +13209,7 @@
       <c r="N191" s="17">
         <v>35.1</v>
       </c>
-      <c r="O191" s="59">
+      <c r="O191" s="58">
         <v>9.0782402811323486</v>
       </c>
       <c r="P191" s="43">
@@ -13236,7 +13230,7 @@
       <c r="U191" s="45">
         <v>18502.589241116122</v>
       </c>
-      <c r="V191" s="131">
+      <c r="V191" s="130">
         <v>792572</v>
       </c>
     </row>
@@ -13268,7 +13262,7 @@
       <c r="I192" s="21">
         <v>2197821</v>
       </c>
-      <c r="J192" s="62">
+      <c r="J192" s="61">
         <v>6</v>
       </c>
       <c r="K192" s="9">
@@ -13283,7 +13277,7 @@
       <c r="N192" s="17">
         <v>36.200000000000003</v>
       </c>
-      <c r="O192" s="59">
+      <c r="O192" s="58">
         <v>6.9670095543216943</v>
       </c>
       <c r="P192" s="43">
@@ -13304,7 +13298,7 @@
       <c r="U192" s="45">
         <v>27345.699933075011</v>
       </c>
-      <c r="V192" s="131">
+      <c r="V192" s="130">
         <v>952577</v>
       </c>
     </row>
@@ -13336,7 +13330,7 @@
       <c r="I193" s="21">
         <v>2593341</v>
       </c>
-      <c r="J193" s="62">
+      <c r="J193" s="61">
         <v>12</v>
       </c>
       <c r="K193" s="9">
@@ -13351,7 +13345,7 @@
       <c r="N193" s="17">
         <v>39.4</v>
       </c>
-      <c r="O193" s="59">
+      <c r="O193" s="58">
         <v>5.9075529318659745</v>
       </c>
       <c r="P193" s="43">
@@ -13372,7 +13366,7 @@
       <c r="U193" s="45">
         <v>23480.451689880498</v>
       </c>
-      <c r="V193" s="131">
+      <c r="V193" s="130">
         <v>1149859</v>
       </c>
     </row>
@@ -13404,7 +13398,7 @@
       <c r="I194" s="21">
         <v>4481611</v>
       </c>
-      <c r="J194" s="62">
+      <c r="J194" s="61">
         <v>11</v>
       </c>
       <c r="K194" s="9">
@@ -13419,7 +13413,7 @@
       <c r="N194" s="17">
         <v>39</v>
       </c>
-      <c r="O194" s="59">
+      <c r="O194" s="58">
         <v>8.49311538158174</v>
       </c>
       <c r="P194" s="43">
@@ -13440,7 +13434,7 @@
       <c r="U194" s="45">
         <v>26553.448884603891</v>
       </c>
-      <c r="V194" s="131">
+      <c r="V194" s="130">
         <v>865866</v>
       </c>
     </row>
@@ -13472,7 +13466,7 @@
       <c r="I195" s="21">
         <v>3416989</v>
       </c>
-      <c r="J195" s="62">
+      <c r="J195" s="61">
         <v>14</v>
       </c>
       <c r="K195" s="9">
@@ -13487,7 +13481,7 @@
       <c r="N195" s="17">
         <v>37.6</v>
       </c>
-      <c r="O195" s="59">
+      <c r="O195" s="58">
         <v>8.9</v>
       </c>
       <c r="P195" s="43">
@@ -13508,7 +13502,7 @@
       <c r="U195" s="45">
         <v>31905.616524927886</v>
       </c>
-      <c r="V195" s="131">
+      <c r="V195" s="130">
         <v>981248</v>
       </c>
     </row>
@@ -13540,7 +13534,7 @@
       <c r="I196" s="21">
         <v>3793588</v>
       </c>
-      <c r="J196" s="62">
+      <c r="J196" s="61">
         <v>5</v>
       </c>
       <c r="K196" s="9">
@@ -13555,7 +13549,7 @@
       <c r="N196" s="17">
         <v>40.1</v>
       </c>
-      <c r="O196" s="59">
+      <c r="O196" s="58">
         <v>8.4</v>
       </c>
       <c r="P196" s="43">
@@ -13576,7 +13570,7 @@
       <c r="U196" s="45">
         <v>27774.736544147465</v>
       </c>
-      <c r="V196" s="131">
+      <c r="V196" s="130">
         <v>957231</v>
       </c>
     </row>
@@ -13608,7 +13602,7 @@
       <c r="I197" s="21">
         <v>2792657</v>
       </c>
-      <c r="J197" s="62">
+      <c r="J197" s="61">
         <v>8</v>
       </c>
       <c r="K197" s="9">
@@ -13623,7 +13617,7 @@
       <c r="N197" s="17">
         <v>52.1</v>
       </c>
-      <c r="O197" s="59">
+      <c r="O197" s="58">
         <v>7.5</v>
       </c>
       <c r="P197" s="43">
@@ -13644,7 +13638,7 @@
       <c r="U197" s="45">
         <v>32544</v>
       </c>
-      <c r="V197" s="131">
+      <c r="V197" s="130">
         <v>1204196</v>
       </c>
     </row>
@@ -13676,7 +13670,7 @@
       <c r="I198" s="21">
         <v>2169458</v>
       </c>
-      <c r="J198" s="62">
+      <c r="J198" s="61">
         <v>9</v>
       </c>
       <c r="K198" s="9">
@@ -13691,7 +13685,7 @@
       <c r="N198" s="17">
         <v>60.4</v>
       </c>
-      <c r="O198" s="59">
+      <c r="O198" s="58">
         <v>7.6</v>
       </c>
       <c r="P198" s="43">
@@ -13712,7 +13706,7 @@
       <c r="U198" s="45">
         <v>36059</v>
       </c>
-      <c r="V198" s="131">
+      <c r="V198" s="130">
         <v>1182902</v>
       </c>
     </row>
@@ -13744,7 +13738,7 @@
       <c r="I199" s="21">
         <v>5066791</v>
       </c>
-      <c r="J199" s="62">
+      <c r="J199" s="61">
         <v>11</v>
       </c>
       <c r="K199" s="9">
@@ -13759,7 +13753,7 @@
       <c r="N199" s="17">
         <v>57</v>
       </c>
-      <c r="O199" s="59">
+      <c r="O199" s="58">
         <v>9</v>
       </c>
       <c r="P199" s="43">
@@ -13780,7 +13774,7 @@
       <c r="U199" s="45">
         <v>38383</v>
       </c>
-      <c r="V199" s="131">
+      <c r="V199" s="130">
         <v>1429539</v>
       </c>
     </row>
@@ -13788,31 +13782,31 @@
       <c r="A200" s="1">
         <v>2025.11</v>
       </c>
-      <c r="B200" s="97">
-        <v>0</v>
-      </c>
-      <c r="C200" s="98">
+      <c r="B200" s="96">
+        <v>0</v>
+      </c>
+      <c r="C200" s="97">
         <v>372911</v>
       </c>
-      <c r="D200" s="98">
+      <c r="D200" s="97">
         <v>4440371</v>
       </c>
-      <c r="E200" s="98">
+      <c r="E200" s="97">
         <v>1003733</v>
       </c>
-      <c r="F200" s="98">
+      <c r="F200" s="97">
         <v>1080928</v>
       </c>
-      <c r="G200" s="98">
-        <v>0</v>
-      </c>
-      <c r="H200" s="99">
+      <c r="G200" s="97">
+        <v>0</v>
+      </c>
+      <c r="H200" s="98">
         <v>36658</v>
       </c>
       <c r="I200" s="21">
         <v>6934602</v>
       </c>
-      <c r="J200" s="62">
+      <c r="J200" s="61">
         <v>16</v>
       </c>
       <c r="K200" s="9">
@@ -13827,7 +13821,7 @@
       <c r="N200" s="17">
         <v>43.4</v>
       </c>
-      <c r="O200" s="59">
+      <c r="O200" s="58">
         <v>9</v>
       </c>
       <c r="P200" s="43">
@@ -13848,7 +13842,7 @@
       <c r="U200" s="45">
         <v>36658</v>
       </c>
-      <c r="V200" s="131">
+      <c r="V200" s="130">
         <v>1570676</v>
       </c>
     </row>
@@ -13856,31 +13850,31 @@
       <c r="A201" s="1">
         <v>2025.12</v>
       </c>
-      <c r="B201" s="97">
+      <c r="B201" s="96">
         <v>77906</v>
       </c>
-      <c r="C201" s="98">
+      <c r="C201" s="97">
         <v>198507</v>
       </c>
       <c r="D201" s="9">
         <v>1948491</v>
       </c>
-      <c r="E201" s="98">
+      <c r="E201" s="97">
         <v>988084</v>
       </c>
-      <c r="F201" s="98">
+      <c r="F201" s="97">
         <v>1312247</v>
       </c>
       <c r="G201" s="9">
         <v>0</v>
       </c>
-      <c r="H201" s="99">
+      <c r="H201" s="98">
         <v>44014</v>
       </c>
       <c r="I201" s="21">
         <v>4569249</v>
       </c>
-      <c r="J201" s="62">
+      <c r="J201" s="61">
         <v>16</v>
       </c>
       <c r="K201" s="9">
@@ -13895,7 +13889,7 @@
       <c r="N201" s="17">
         <v>35.799999999999997</v>
       </c>
-      <c r="O201" s="59">
+      <c r="O201" s="58">
         <v>8.9</v>
       </c>
       <c r="P201" s="43">
@@ -13916,11 +13910,11 @@
       <c r="U201" s="45">
         <v>44014</v>
       </c>
-      <c r="V201" s="131">
+      <c r="V201" s="130">
         <v>1855783</v>
       </c>
-      <c r="W201" s="100"/>
-      <c r="X201" s="101"/>
+      <c r="W201" s="99"/>
+      <c r="X201" s="100"/>
     </row>
     <row r="202" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
@@ -13950,7 +13944,7 @@
       <c r="I202" s="21">
         <v>5586047</v>
       </c>
-      <c r="J202" s="62">
+      <c r="J202" s="61">
         <v>10</v>
       </c>
       <c r="K202" s="9">
@@ -13965,7 +13959,7 @@
       <c r="N202" s="17">
         <v>36.9</v>
       </c>
-      <c r="O202" s="59">
+      <c r="O202" s="58">
         <v>7</v>
       </c>
       <c r="P202" s="43">
@@ -13986,7 +13980,7 @@
       <c r="U202" s="45">
         <v>45846</v>
       </c>
-      <c r="V202" s="131">
+      <c r="V202" s="130">
         <v>1586833</v>
       </c>
     </row>
@@ -14018,7 +14012,7 @@
       <c r="I203" s="21">
         <v>3656034</v>
       </c>
-      <c r="J203" s="62">
+      <c r="J203" s="61">
         <v>8</v>
       </c>
       <c r="K203" s="9">
@@ -14033,7 +14027,7 @@
       <c r="N203" s="17">
         <v>37.799999999999997</v>
       </c>
-      <c r="O203" s="59">
+      <c r="O203" s="58">
         <v>8.1999999999999993</v>
       </c>
       <c r="P203" s="43">
@@ -14054,7 +14048,7 @@
       <c r="U203" s="45">
         <v>50748</v>
       </c>
-      <c r="V203" s="131">
+      <c r="V203" s="130">
         <v>1489876</v>
       </c>
     </row>
@@ -14086,7 +14080,7 @@
       <c r="I204" s="21">
         <v>3127441</v>
       </c>
-      <c r="J204" s="62">
+      <c r="J204" s="61">
         <v>9</v>
       </c>
       <c r="K204" s="9">
@@ -14101,7 +14095,7 @@
       <c r="N204" s="17">
         <v>34.1</v>
       </c>
-      <c r="O204" s="59">
+      <c r="O204" s="58">
         <v>7.4</v>
       </c>
       <c r="P204" s="43">
@@ -14122,7 +14116,7 @@
       <c r="U204" s="45">
         <v>61454</v>
       </c>
-      <c r="V204" s="131">
+      <c r="V204" s="130">
         <v>1760388</v>
       </c>
     </row>
@@ -14154,7 +14148,7 @@
       <c r="I205" s="21">
         <v>5119796</v>
       </c>
-      <c r="J205" s="62">
+      <c r="J205" s="61">
         <v>15</v>
       </c>
       <c r="K205" s="9">
@@ -14169,7 +14163,7 @@
       <c r="N205" s="17">
         <v>30.4</v>
       </c>
-      <c r="O205" s="59">
+      <c r="O205" s="58">
         <v>6.8</v>
       </c>
       <c r="P205" s="43">
@@ -14190,10 +14184,10 @@
       <c r="U205" s="45">
         <v>58144</v>
       </c>
-      <c r="V205" s="131">
+      <c r="V205" s="130">
         <v>1546733</v>
       </c>
-      <c r="W205" s="102"/>
+      <c r="W205" s="101"/>
     </row>
     <row r="206" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
@@ -14223,7 +14217,7 @@
       <c r="I206" s="21">
         <v>5270362</v>
       </c>
-      <c r="J206" s="62">
+      <c r="J206" s="61">
         <v>9</v>
       </c>
       <c r="K206" s="9">
@@ -14238,7 +14232,7 @@
       <c r="N206" s="17">
         <v>28.2</v>
       </c>
-      <c r="O206" s="59">
+      <c r="O206" s="58">
         <v>6.9</v>
       </c>
       <c r="P206" s="43">
@@ -14259,7 +14253,7 @@
       <c r="U206" s="45">
         <v>53040</v>
       </c>
-      <c r="V206" s="131">
+      <c r="V206" s="130">
         <v>1760235</v>
       </c>
     </row>
@@ -14291,7 +14285,7 @@
       <c r="I207" s="21">
         <v>6305112</v>
       </c>
-      <c r="J207" s="62">
+      <c r="J207" s="61">
         <v>13</v>
       </c>
       <c r="K207" s="9">
@@ -14306,7 +14300,7 @@
       <c r="N207" s="17">
         <v>26.8</v>
       </c>
-      <c r="O207" s="59">
+      <c r="O207" s="58">
         <v>6.9</v>
       </c>
       <c r="P207" s="43">
@@ -14327,7 +14321,7 @@
       <c r="U207" s="45">
         <v>72429</v>
       </c>
-      <c r="V207" s="131">
+      <c r="V207" s="130">
         <v>2066029</v>
       </c>
     </row>
@@ -14359,7 +14353,7 @@
       <c r="I208" s="21">
         <v>5278443</v>
       </c>
-      <c r="J208" s="62">
+      <c r="J208" s="61">
         <v>14</v>
       </c>
       <c r="K208" s="9">
@@ -14374,7 +14368,7 @@
       <c r="N208" s="17">
         <v>27</v>
       </c>
-      <c r="O208" s="59">
+      <c r="O208" s="58">
         <v>6.3</v>
       </c>
       <c r="P208" s="43">
@@ -14395,7 +14389,7 @@
       <c r="U208" s="45">
         <v>68667</v>
       </c>
-      <c r="V208" s="131">
+      <c r="V208" s="130">
         <v>1881744</v>
       </c>
     </row>
@@ -14427,7 +14421,7 @@
       <c r="I209" s="21">
         <v>4495487</v>
       </c>
-      <c r="J209" s="62">
+      <c r="J209" s="61">
         <v>10</v>
       </c>
       <c r="K209" s="9">
@@ -14442,7 +14436,7 @@
       <c r="N209" s="17">
         <v>28.5</v>
       </c>
-      <c r="O209" s="59">
+      <c r="O209" s="58">
         <v>6.9</v>
       </c>
       <c r="P209" s="43">
@@ -14463,7 +14457,7 @@
       <c r="U209" s="45">
         <v>59065</v>
       </c>
-      <c r="V209" s="131">
+      <c r="V209" s="130">
         <v>1792387</v>
       </c>
     </row>
@@ -14471,68 +14465,68 @@
       <c r="A210" s="1">
         <v>2026.09</v>
       </c>
-      <c r="B210" s="46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C210" s="9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D210" s="9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E210" s="9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F210" s="9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G210" s="9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H210" s="9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I210" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J210" s="62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K210" s="9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L210" s="21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M210" s="24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N210" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O210" s="59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P210" s="43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q210" s="44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R210" s="44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S210" s="44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T210" s="44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U210" s="45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V210" s="131" t="e">
-        <v>#N/A</v>
+      <c r="B210" s="46">
+        <v>0</v>
+      </c>
+      <c r="C210" s="9">
+        <v>310915</v>
+      </c>
+      <c r="D210" s="9">
+        <v>4399299</v>
+      </c>
+      <c r="E210" s="9">
+        <v>1312381</v>
+      </c>
+      <c r="F210" s="9">
+        <v>1355283</v>
+      </c>
+      <c r="G210" s="9">
+        <v>0</v>
+      </c>
+      <c r="H210" s="9">
+        <v>59484</v>
+      </c>
+      <c r="I210" s="21">
+        <v>7437360</v>
+      </c>
+      <c r="J210" s="61">
+        <v>17</v>
+      </c>
+      <c r="K210" s="9">
+        <v>43</v>
+      </c>
+      <c r="L210" s="21">
+        <v>0</v>
+      </c>
+      <c r="M210" s="24">
+        <v>990</v>
+      </c>
+      <c r="N210" s="17">
+        <v>28.4</v>
+      </c>
+      <c r="O210" s="58">
+        <v>6.9</v>
+      </c>
+      <c r="P210" s="43">
+        <v>51029</v>
+      </c>
+      <c r="Q210" s="44">
+        <v>43815</v>
+      </c>
+      <c r="R210" s="44">
+        <v>334046</v>
+      </c>
+      <c r="S210" s="44">
+        <v>181128</v>
+      </c>
+      <c r="T210" s="44">
+        <v>1355283</v>
+      </c>
+      <c r="U210" s="45">
+        <v>59484</v>
+      </c>
+      <c r="V210" s="130">
+        <v>2024785</v>
       </c>
     </row>
     <row r="211" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -14563,7 +14557,7 @@
       <c r="I211" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J211" s="62" t="e">
+      <c r="J211" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K211" s="9" t="e">
@@ -14578,7 +14572,7 @@
       <c r="N211" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O211" s="59" t="e">
+      <c r="O211" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P211" s="43" t="e">
@@ -14599,7 +14593,7 @@
       <c r="U211" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V211" s="131" t="e">
+      <c r="V211" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -14631,7 +14625,7 @@
       <c r="I212" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J212" s="62" t="e">
+      <c r="J212" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K212" s="9" t="e">
@@ -14646,7 +14640,7 @@
       <c r="N212" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O212" s="59" t="e">
+      <c r="O212" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P212" s="43" t="e">
@@ -14667,7 +14661,7 @@
       <c r="U212" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V212" s="131" t="e">
+      <c r="V212" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -14699,7 +14693,7 @@
       <c r="I213" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J213" s="62" t="e">
+      <c r="J213" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K213" s="9" t="e">
@@ -14714,7 +14708,7 @@
       <c r="N213" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O213" s="59" t="e">
+      <c r="O213" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P213" s="43" t="e">
@@ -14735,7 +14729,7 @@
       <c r="U213" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V213" s="131" t="e">
+      <c r="V213" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -14767,7 +14761,7 @@
       <c r="I214" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J214" s="62" t="e">
+      <c r="J214" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K214" s="9" t="e">
@@ -14782,7 +14776,7 @@
       <c r="N214" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O214" s="59" t="e">
+      <c r="O214" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P214" s="43" t="e">
@@ -14803,7 +14797,7 @@
       <c r="U214" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V214" s="131" t="e">
+      <c r="V214" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -14835,7 +14829,7 @@
       <c r="I215" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J215" s="62" t="e">
+      <c r="J215" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K215" s="9" t="e">
@@ -14850,7 +14844,7 @@
       <c r="N215" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O215" s="59" t="e">
+      <c r="O215" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P215" s="43" t="e">
@@ -14871,7 +14865,7 @@
       <c r="U215" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V215" s="131" t="e">
+      <c r="V215" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -14903,7 +14897,7 @@
       <c r="I216" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J216" s="62" t="e">
+      <c r="J216" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K216" s="9" t="e">
@@ -14918,7 +14912,7 @@
       <c r="N216" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O216" s="59" t="e">
+      <c r="O216" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P216" s="43" t="e">
@@ -14939,7 +14933,7 @@
       <c r="U216" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V216" s="131" t="e">
+      <c r="V216" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -14971,7 +14965,7 @@
       <c r="I217" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J217" s="62" t="e">
+      <c r="J217" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K217" s="9" t="e">
@@ -14986,7 +14980,7 @@
       <c r="N217" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O217" s="59" t="e">
+      <c r="O217" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P217" s="43" t="e">
@@ -15007,7 +15001,7 @@
       <c r="U217" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V217" s="131" t="e">
+      <c r="V217" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15039,7 +15033,7 @@
       <c r="I218" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J218" s="62" t="e">
+      <c r="J218" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K218" s="9" t="e">
@@ -15054,7 +15048,7 @@
       <c r="N218" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O218" s="59" t="e">
+      <c r="O218" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P218" s="43" t="e">
@@ -15075,7 +15069,7 @@
       <c r="U218" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V218" s="131" t="e">
+      <c r="V218" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15107,7 +15101,7 @@
       <c r="I219" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J219" s="62" t="e">
+      <c r="J219" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K219" s="9" t="e">
@@ -15122,7 +15116,7 @@
       <c r="N219" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O219" s="59" t="e">
+      <c r="O219" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P219" s="43" t="e">
@@ -15143,7 +15137,7 @@
       <c r="U219" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V219" s="131" t="e">
+      <c r="V219" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15175,7 +15169,7 @@
       <c r="I220" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J220" s="62" t="e">
+      <c r="J220" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K220" s="9" t="e">
@@ -15190,7 +15184,7 @@
       <c r="N220" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O220" s="59" t="e">
+      <c r="O220" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P220" s="43" t="e">
@@ -15211,7 +15205,7 @@
       <c r="U220" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V220" s="131" t="e">
+      <c r="V220" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15243,7 +15237,7 @@
       <c r="I221" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J221" s="62" t="e">
+      <c r="J221" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K221" s="9" t="e">
@@ -15258,7 +15252,7 @@
       <c r="N221" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O221" s="59" t="e">
+      <c r="O221" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P221" s="43" t="e">
@@ -15279,7 +15273,7 @@
       <c r="U221" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V221" s="131" t="e">
+      <c r="V221" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15311,7 +15305,7 @@
       <c r="I222" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J222" s="62" t="e">
+      <c r="J222" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K222" s="9" t="e">
@@ -15326,7 +15320,7 @@
       <c r="N222" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O222" s="59" t="e">
+      <c r="O222" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P222" s="43" t="e">
@@ -15347,7 +15341,7 @@
       <c r="U222" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V222" s="131" t="e">
+      <c r="V222" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15379,7 +15373,7 @@
       <c r="I223" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J223" s="62" t="e">
+      <c r="J223" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K223" s="9" t="e">
@@ -15394,7 +15388,7 @@
       <c r="N223" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O223" s="59" t="e">
+      <c r="O223" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P223" s="43" t="e">
@@ -15415,7 +15409,7 @@
       <c r="U223" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V223" s="131" t="e">
+      <c r="V223" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15447,7 +15441,7 @@
       <c r="I224" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J224" s="62" t="e">
+      <c r="J224" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K224" s="9" t="e">
@@ -15462,7 +15456,7 @@
       <c r="N224" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O224" s="59" t="e">
+      <c r="O224" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P224" s="43" t="e">
@@ -15483,7 +15477,7 @@
       <c r="U224" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V224" s="131" t="e">
+      <c r="V224" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15515,7 +15509,7 @@
       <c r="I225" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J225" s="62" t="e">
+      <c r="J225" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K225" s="9" t="e">
@@ -15530,7 +15524,7 @@
       <c r="N225" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O225" s="59" t="e">
+      <c r="O225" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P225" s="43" t="e">
@@ -15551,7 +15545,7 @@
       <c r="U225" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V225" s="131" t="e">
+      <c r="V225" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15583,7 +15577,7 @@
       <c r="I226" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J226" s="62" t="e">
+      <c r="J226" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K226" s="9" t="e">
@@ -15598,7 +15592,7 @@
       <c r="N226" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O226" s="59" t="e">
+      <c r="O226" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P226" s="43" t="e">
@@ -15619,7 +15613,7 @@
       <c r="U226" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V226" s="131" t="e">
+      <c r="V226" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15651,7 +15645,7 @@
       <c r="I227" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J227" s="62" t="e">
+      <c r="J227" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K227" s="9" t="e">
@@ -15666,7 +15660,7 @@
       <c r="N227" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O227" s="59" t="e">
+      <c r="O227" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P227" s="43" t="e">
@@ -15687,7 +15681,7 @@
       <c r="U227" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V227" s="131" t="e">
+      <c r="V227" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15719,7 +15713,7 @@
       <c r="I228" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J228" s="62" t="e">
+      <c r="J228" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K228" s="9" t="e">
@@ -15734,7 +15728,7 @@
       <c r="N228" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O228" s="59" t="e">
+      <c r="O228" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P228" s="43" t="e">
@@ -15755,7 +15749,7 @@
       <c r="U228" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V228" s="131" t="e">
+      <c r="V228" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15787,7 +15781,7 @@
       <c r="I229" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J229" s="62" t="e">
+      <c r="J229" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K229" s="9" t="e">
@@ -15802,7 +15796,7 @@
       <c r="N229" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O229" s="59" t="e">
+      <c r="O229" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P229" s="43" t="e">
@@ -15823,7 +15817,7 @@
       <c r="U229" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V229" s="131" t="e">
+      <c r="V229" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15855,7 +15849,7 @@
       <c r="I230" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J230" s="62" t="e">
+      <c r="J230" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K230" s="9" t="e">
@@ -15870,7 +15864,7 @@
       <c r="N230" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O230" s="59" t="e">
+      <c r="O230" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P230" s="43" t="e">
@@ -15891,7 +15885,7 @@
       <c r="U230" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V230" s="131" t="e">
+      <c r="V230" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15923,7 +15917,7 @@
       <c r="I231" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J231" s="62" t="e">
+      <c r="J231" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K231" s="9" t="e">
@@ -15938,7 +15932,7 @@
       <c r="N231" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O231" s="59" t="e">
+      <c r="O231" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P231" s="43" t="e">
@@ -15959,7 +15953,7 @@
       <c r="U231" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V231" s="131" t="e">
+      <c r="V231" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15991,7 +15985,7 @@
       <c r="I232" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J232" s="62" t="e">
+      <c r="J232" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K232" s="9" t="e">
@@ -16006,7 +16000,7 @@
       <c r="N232" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O232" s="59" t="e">
+      <c r="O232" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P232" s="43" t="e">
@@ -16027,7 +16021,7 @@
       <c r="U232" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V232" s="131" t="e">
+      <c r="V232" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -16059,7 +16053,7 @@
       <c r="I233" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J233" s="62" t="e">
+      <c r="J233" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K233" s="9" t="e">
@@ -16074,7 +16068,7 @@
       <c r="N233" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O233" s="59" t="e">
+      <c r="O233" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P233" s="43" t="e">
@@ -16095,7 +16089,7 @@
       <c r="U233" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V233" s="131" t="e">
+      <c r="V233" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -16127,7 +16121,7 @@
       <c r="I234" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J234" s="62" t="e">
+      <c r="J234" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K234" s="9" t="e">
@@ -16142,7 +16136,7 @@
       <c r="N234" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O234" s="59" t="e">
+      <c r="O234" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P234" s="43" t="e">
@@ -16163,7 +16157,7 @@
       <c r="U234" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V234" s="131" t="e">
+      <c r="V234" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -16195,7 +16189,7 @@
       <c r="I235" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J235" s="62" t="e">
+      <c r="J235" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K235" s="9" t="e">
@@ -16210,7 +16204,7 @@
       <c r="N235" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O235" s="59" t="e">
+      <c r="O235" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P235" s="43" t="e">
@@ -16231,7 +16225,7 @@
       <c r="U235" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V235" s="131" t="e">
+      <c r="V235" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -16263,7 +16257,7 @@
       <c r="I236" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J236" s="62" t="e">
+      <c r="J236" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K236" s="9" t="e">
@@ -16278,7 +16272,7 @@
       <c r="N236" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O236" s="59" t="e">
+      <c r="O236" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P236" s="43" t="e">
@@ -16299,7 +16293,7 @@
       <c r="U236" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V236" s="131" t="e">
+      <c r="V236" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -16331,7 +16325,7 @@
       <c r="I237" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J237" s="62" t="e">
+      <c r="J237" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K237" s="9" t="e">
@@ -16346,7 +16340,7 @@
       <c r="N237" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O237" s="59" t="e">
+      <c r="O237" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P237" s="43" t="e">
@@ -16367,7 +16361,7 @@
       <c r="U237" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V237" s="131" t="e">
+      <c r="V237" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -16399,7 +16393,7 @@
       <c r="I238" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J238" s="62" t="e">
+      <c r="J238" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K238" s="9" t="e">
@@ -16414,7 +16408,7 @@
       <c r="N238" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O238" s="59" t="e">
+      <c r="O238" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P238" s="43" t="e">
@@ -16435,7 +16429,7 @@
       <c r="U238" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V238" s="131" t="e">
+      <c r="V238" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -16467,7 +16461,7 @@
       <c r="I239" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J239" s="62" t="e">
+      <c r="J239" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K239" s="9" t="e">
@@ -16482,7 +16476,7 @@
       <c r="N239" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O239" s="59" t="e">
+      <c r="O239" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P239" s="43" t="e">
@@ -16503,7 +16497,7 @@
       <c r="U239" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V239" s="131" t="e">
+      <c r="V239" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -16535,7 +16529,7 @@
       <c r="I240" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J240" s="62" t="e">
+      <c r="J240" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K240" s="9" t="e">
@@ -16550,7 +16544,7 @@
       <c r="N240" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O240" s="59" t="e">
+      <c r="O240" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P240" s="43" t="e">
@@ -16571,7 +16565,7 @@
       <c r="U240" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V240" s="131" t="e">
+      <c r="V240" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -16603,7 +16597,7 @@
       <c r="I241" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J241" s="62" t="e">
+      <c r="J241" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K241" s="9" t="e">
@@ -16618,7 +16612,7 @@
       <c r="N241" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O241" s="59" t="e">
+      <c r="O241" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P241" s="43" t="e">
@@ -16639,7 +16633,7 @@
       <c r="U241" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V241" s="131" t="e">
+      <c r="V241" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -16671,7 +16665,7 @@
       <c r="I242" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J242" s="62" t="e">
+      <c r="J242" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K242" s="9" t="e">
@@ -16686,7 +16680,7 @@
       <c r="N242" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O242" s="59" t="e">
+      <c r="O242" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P242" s="43" t="e">
@@ -16707,7 +16701,7 @@
       <c r="U242" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V242" s="131" t="e">
+      <c r="V242" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -16739,7 +16733,7 @@
       <c r="I243" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J243" s="62" t="e">
+      <c r="J243" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K243" s="9" t="e">
@@ -16754,7 +16748,7 @@
       <c r="N243" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O243" s="59" t="e">
+      <c r="O243" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P243" s="43" t="e">
@@ -16775,7 +16769,7 @@
       <c r="U243" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V243" s="131" t="e">
+      <c r="V243" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -16807,7 +16801,7 @@
       <c r="I244" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J244" s="62" t="e">
+      <c r="J244" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K244" s="9" t="e">
@@ -16822,7 +16816,7 @@
       <c r="N244" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O244" s="59" t="e">
+      <c r="O244" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P244" s="43" t="e">
@@ -16843,7 +16837,7 @@
       <c r="U244" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V244" s="131" t="e">
+      <c r="V244" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -16875,7 +16869,7 @@
       <c r="I245" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J245" s="62" t="e">
+      <c r="J245" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K245" s="9" t="e">
@@ -16890,7 +16884,7 @@
       <c r="N245" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O245" s="59" t="e">
+      <c r="O245" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P245" s="43" t="e">
@@ -16911,7 +16905,7 @@
       <c r="U245" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V245" s="131" t="e">
+      <c r="V245" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -16943,7 +16937,7 @@
       <c r="I246" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J246" s="62" t="e">
+      <c r="J246" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K246" s="9" t="e">
@@ -16958,7 +16952,7 @@
       <c r="N246" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O246" s="59" t="e">
+      <c r="O246" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P246" s="43" t="e">
@@ -16979,7 +16973,7 @@
       <c r="U246" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V246" s="131" t="e">
+      <c r="V246" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -17011,7 +17005,7 @@
       <c r="I247" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J247" s="62" t="e">
+      <c r="J247" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K247" s="9" t="e">
@@ -17026,7 +17020,7 @@
       <c r="N247" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O247" s="59" t="e">
+      <c r="O247" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P247" s="43" t="e">
@@ -17047,7 +17041,7 @@
       <c r="U247" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V247" s="131" t="e">
+      <c r="V247" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -17079,7 +17073,7 @@
       <c r="I248" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J248" s="62" t="e">
+      <c r="J248" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K248" s="9" t="e">
@@ -17094,7 +17088,7 @@
       <c r="N248" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O248" s="59" t="e">
+      <c r="O248" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P248" s="43" t="e">
@@ -17115,7 +17109,7 @@
       <c r="U248" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V248" s="131" t="e">
+      <c r="V248" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -17147,7 +17141,7 @@
       <c r="I249" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J249" s="62" t="e">
+      <c r="J249" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K249" s="9" t="e">
@@ -17162,7 +17156,7 @@
       <c r="N249" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O249" s="59" t="e">
+      <c r="O249" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P249" s="43" t="e">
@@ -17183,7 +17177,7 @@
       <c r="U249" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V249" s="131" t="e">
+      <c r="V249" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -17215,7 +17209,7 @@
       <c r="I250" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J250" s="62" t="e">
+      <c r="J250" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K250" s="9" t="e">
@@ -17230,7 +17224,7 @@
       <c r="N250" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O250" s="59" t="e">
+      <c r="O250" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P250" s="43" t="e">
@@ -17251,7 +17245,7 @@
       <c r="U250" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V250" s="131" t="e">
+      <c r="V250" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -17283,7 +17277,7 @@
       <c r="I251" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J251" s="62" t="e">
+      <c r="J251" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K251" s="9" t="e">
@@ -17298,7 +17292,7 @@
       <c r="N251" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O251" s="59" t="e">
+      <c r="O251" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P251" s="43" t="e">
@@ -17319,7 +17313,7 @@
       <c r="U251" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V251" s="131" t="e">
+      <c r="V251" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -17351,7 +17345,7 @@
       <c r="I252" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J252" s="62" t="e">
+      <c r="J252" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K252" s="9" t="e">
@@ -17366,7 +17360,7 @@
       <c r="N252" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O252" s="59" t="e">
+      <c r="O252" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P252" s="43" t="e">
@@ -17387,7 +17381,7 @@
       <c r="U252" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V252" s="131" t="e">
+      <c r="V252" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -17419,7 +17413,7 @@
       <c r="I253" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J253" s="62" t="e">
+      <c r="J253" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K253" s="9" t="e">
@@ -17434,7 +17428,7 @@
       <c r="N253" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O253" s="59" t="e">
+      <c r="O253" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P253" s="43" t="e">
@@ -17455,7 +17449,7 @@
       <c r="U253" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V253" s="131" t="e">
+      <c r="V253" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -17487,7 +17481,7 @@
       <c r="I254" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J254" s="62" t="e">
+      <c r="J254" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K254" s="9" t="e">
@@ -17502,7 +17496,7 @@
       <c r="N254" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O254" s="59" t="e">
+      <c r="O254" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P254" s="43" t="e">
@@ -17523,7 +17517,7 @@
       <c r="U254" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V254" s="131" t="e">
+      <c r="V254" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -17555,7 +17549,7 @@
       <c r="I255" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J255" s="62" t="e">
+      <c r="J255" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K255" s="9" t="e">
@@ -17570,7 +17564,7 @@
       <c r="N255" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O255" s="59" t="e">
+      <c r="O255" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P255" s="43" t="e">
@@ -17591,7 +17585,7 @@
       <c r="U255" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V255" s="131" t="e">
+      <c r="V255" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -17623,7 +17617,7 @@
       <c r="I256" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J256" s="62" t="e">
+      <c r="J256" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K256" s="9" t="e">
@@ -17638,7 +17632,7 @@
       <c r="N256" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O256" s="59" t="e">
+      <c r="O256" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P256" s="43" t="e">
@@ -17659,7 +17653,7 @@
       <c r="U256" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V256" s="131" t="e">
+      <c r="V256" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -17691,7 +17685,7 @@
       <c r="I257" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J257" s="62" t="e">
+      <c r="J257" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K257" s="9" t="e">
@@ -17706,7 +17700,7 @@
       <c r="N257" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O257" s="59" t="e">
+      <c r="O257" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P257" s="43" t="e">
@@ -17727,7 +17721,7 @@
       <c r="U257" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V257" s="131" t="e">
+      <c r="V257" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -17759,7 +17753,7 @@
       <c r="I258" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J258" s="62" t="e">
+      <c r="J258" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K258" s="9" t="e">
@@ -17774,7 +17768,7 @@
       <c r="N258" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O258" s="59" t="e">
+      <c r="O258" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P258" s="43" t="e">
@@ -17795,7 +17789,7 @@
       <c r="U258" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V258" s="131" t="e">
+      <c r="V258" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -17827,7 +17821,7 @@
       <c r="I259" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J259" s="62" t="e">
+      <c r="J259" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K259" s="9" t="e">
@@ -17842,7 +17836,7 @@
       <c r="N259" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O259" s="59" t="e">
+      <c r="O259" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P259" s="43" t="e">
@@ -17863,7 +17857,7 @@
       <c r="U259" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V259" s="131" t="e">
+      <c r="V259" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -17895,7 +17889,7 @@
       <c r="I260" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J260" s="62" t="e">
+      <c r="J260" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K260" s="9" t="e">
@@ -17910,7 +17904,7 @@
       <c r="N260" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O260" s="59" t="e">
+      <c r="O260" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P260" s="43" t="e">
@@ -17931,7 +17925,7 @@
       <c r="U260" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V260" s="131" t="e">
+      <c r="V260" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -17963,7 +17957,7 @@
       <c r="I261" s="21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J261" s="62" t="e">
+      <c r="J261" s="61" t="e">
         <v>#N/A</v>
       </c>
       <c r="K261" s="9" t="e">
@@ -17978,7 +17972,7 @@
       <c r="N261" s="17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="O261" s="59" t="e">
+      <c r="O261" s="58" t="e">
         <v>#N/A</v>
       </c>
       <c r="P261" s="43" t="e">
@@ -17999,15 +17993,12 @@
       <c r="U261" s="45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V261" s="131" t="e">
+      <c r="V261" s="130" t="e">
         <v>#N/A</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Índice!A13" display="Volver al índice" xr:uid="{0C48BE73-9842-4B71-B11F-E29753946939}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -18215,6 +18206,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
@@ -18223,15 +18223,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18254,6 +18245,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA7A1AE2-79B5-45E2-9D53-11A870F1D987}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A87D32-22F8-4B25-9692-D498E7E5A8B0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -18262,12 +18261,4 @@
     <ds:schemaRef ds:uri="b5dd4176-d247-4204-85b8-921214f3ccea"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA7A1AE2-79B5-45E2-9D53-11A870F1D987}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>